--- a/158/prob158.xlsx
+++ b/158/prob158.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G4" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00014</v>
+        <v>0.00025</v>
       </c>
       <c r="H4" s="30" t="s">
         <v>21</v>
@@ -3099,14 +3099,14 @@
       </c>
       <c r="E5" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.598</v>
+        <v>0.608</v>
       </c>
       <c r="F5" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>9E-005</v>
+        <v>0.00023</v>
       </c>
       <c r="H5" s="30" t="s">
         <v>21</v>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="E6" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.589</v>
+        <v>0.441</v>
       </c>
       <c r="F6" s="33" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00023</v>
+        <v>0.00024</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>21</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G7" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00024</v>
+        <v>0.00014</v>
       </c>
       <c r="H7" s="30" t="s">
         <v>21</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="E8" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.548</v>
+        <v>0.509</v>
       </c>
       <c r="F8" s="30" t="n">
         <v>0</v>
@@ -3191,14 +3191,14 @@
       </c>
       <c r="E9" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.483</v>
+        <v>0.551</v>
       </c>
       <c r="F9" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>8E-005</v>
+        <v>0.00021</v>
       </c>
       <c r="H9" s="30" t="s">
         <v>21</v>
@@ -3214,14 +3214,14 @@
       </c>
       <c r="E10" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.512</v>
+        <v>0.492</v>
       </c>
       <c r="F10" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00017</v>
+        <v>9E-005</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>21</v>
@@ -3237,14 +3237,14 @@
       </c>
       <c r="E11" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.591</v>
+        <v>0.445</v>
       </c>
       <c r="F11" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00012</v>
+        <v>0.00016</v>
       </c>
       <c r="H11" s="30" t="s">
         <v>21</v>
@@ -3275,7 +3275,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.61"/>
@@ -3307,6 +3307,24 @@
       <c r="G2" s="11" t="n">
         <v>7</v>
       </c>
+      <c r="K2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
@@ -4582,6 +4600,40 @@
       <c r="P29" s="35" t="n">
         <f aca="false">SUM(P3:P28)</f>
         <v>3946800</v>
+      </c>
+      <c r="Q29" s="0" t="n">
+        <f aca="false">SUM(K29:P29)</f>
+        <v>27012810</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" s="0" t="n">
+        <f aca="false">COMBIN(26,G2)*COMBIN(G2-1,K2-1)</f>
+        <v>3946800</v>
+      </c>
+      <c r="L30" s="0" t="n">
+        <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,L2-1)</f>
+        <v>9867000</v>
+      </c>
+      <c r="M30" s="0" t="n">
+        <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,M2-1)</f>
+        <v>13156000</v>
+      </c>
+      <c r="N30" s="0" t="n">
+        <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,N2-1)</f>
+        <v>9867000</v>
+      </c>
+      <c r="O30" s="0" t="n">
+        <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,O2-1)</f>
+        <v>3946800</v>
+      </c>
+      <c r="P30" s="0" t="n">
+        <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,P2-1)</f>
+        <v>657800</v>
+      </c>
+      <c r="Q30" s="0" t="n">
+        <f aca="false">SUM(K30:P30)</f>
+        <v>41441400</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5219,11 +5271,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U39"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Q39"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="4.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="13" style="0" width="5.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="5.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="5.4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5248,14 +5301,10 @@
       </c>
       <c r="L1" s="38"/>
       <c r="M1" s="39"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23"/>
@@ -5277,14 +5326,10 @@
         <v>6</v>
       </c>
       <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="n">
@@ -5310,18 +5355,14 @@
         <v>6</v>
       </c>
       <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="23" t="n">
+      <c r="N3" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23" t="n">
+      <c r="O3" s="23"/>
+      <c r="P3" s="23" t="n">
         <v>1026</v>
       </c>
-      <c r="U3" s="23"/>
+      <c r="Q3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="n">
@@ -5347,18 +5388,14 @@
         <v>6</v>
       </c>
       <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="23" t="n">
+      <c r="N4" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23" t="n">
+      <c r="O4" s="23"/>
+      <c r="P4" s="23" t="n">
         <v>1140</v>
       </c>
-      <c r="U4" s="23"/>
+      <c r="Q4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="n">
@@ -5384,18 +5421,14 @@
         <v>6</v>
       </c>
       <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="23" t="n">
+      <c r="N5" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23" t="n">
+      <c r="O5" s="23"/>
+      <c r="P5" s="23" t="n">
         <v>1260</v>
       </c>
-      <c r="U5" s="23"/>
+      <c r="Q5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="n">
@@ -5421,18 +5454,14 @@
         <v>6</v>
       </c>
       <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="23" t="n">
+      <c r="N6" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23" t="n">
+      <c r="O6" s="23"/>
+      <c r="P6" s="23" t="n">
         <v>1386</v>
       </c>
-      <c r="U6" s="23"/>
+      <c r="Q6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="n">
@@ -5458,18 +5487,14 @@
         <v>6</v>
       </c>
       <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="23" t="n">
+      <c r="N7" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23" t="n">
+      <c r="O7" s="23"/>
+      <c r="P7" s="23" t="n">
         <v>1386</v>
       </c>
-      <c r="U7" s="23"/>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="n">
@@ -5495,18 +5520,14 @@
         <v>5</v>
       </c>
       <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="23" t="n">
+      <c r="N8" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23" t="n">
+      <c r="O8" s="23"/>
+      <c r="P8" s="23" t="n">
         <v>1026</v>
       </c>
-      <c r="U8" s="23"/>
+      <c r="Q8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23"/>
@@ -5532,18 +5553,14 @@
         <v>5</v>
       </c>
       <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="23"/>
+      <c r="N9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="n">
@@ -5569,18 +5586,14 @@
         <v>5</v>
       </c>
       <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="23" t="n">
+      <c r="N10" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23" t="n">
+      <c r="O10" s="23"/>
+      <c r="P10" s="23" t="n">
         <v>570</v>
       </c>
-      <c r="U10" s="23"/>
+      <c r="Q10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="n">
@@ -5606,18 +5619,14 @@
         <v>5</v>
       </c>
       <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="23" t="n">
+      <c r="N11" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23" t="n">
+      <c r="O11" s="23"/>
+      <c r="P11" s="23" t="n">
         <v>630</v>
       </c>
-      <c r="U11" s="23"/>
+      <c r="Q11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="n">
@@ -5643,18 +5652,14 @@
         <v>5</v>
       </c>
       <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="23" t="n">
+      <c r="N12" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23" t="n">
+      <c r="O12" s="23"/>
+      <c r="P12" s="23" t="n">
         <v>693</v>
       </c>
-      <c r="U12" s="23"/>
+      <c r="Q12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="n">
@@ -5680,18 +5685,14 @@
         <v>5</v>
       </c>
       <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="23" t="n">
+      <c r="N13" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23" t="n">
+      <c r="O13" s="23"/>
+      <c r="P13" s="23" t="n">
         <v>693</v>
       </c>
-      <c r="U13" s="23"/>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="n">
@@ -5717,18 +5718,14 @@
         <v>4</v>
       </c>
       <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="23" t="n">
+      <c r="N14" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23" t="n">
+      <c r="O14" s="23"/>
+      <c r="P14" s="23" t="n">
         <v>693</v>
       </c>
-      <c r="U14" s="23"/>
+      <c r="Q14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="n">
@@ -5754,18 +5751,14 @@
         <v>4</v>
       </c>
       <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="23" t="n">
+      <c r="N15" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23" t="n">
+      <c r="O15" s="23"/>
+      <c r="P15" s="23" t="n">
         <v>513</v>
       </c>
-      <c r="U15" s="23"/>
+      <c r="Q15" s="23"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23"/>
@@ -5791,18 +5784,14 @@
         <v>4</v>
       </c>
       <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="23"/>
+      <c r="N16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="23"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="n">
@@ -5828,18 +5817,14 @@
         <v>4</v>
       </c>
       <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="39"/>
-      <c r="R17" s="23" t="n">
+      <c r="N17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23" t="n">
+      <c r="O17" s="23"/>
+      <c r="P17" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="U17" s="23"/>
+      <c r="Q17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="n">
@@ -5865,18 +5850,14 @@
         <v>4</v>
       </c>
       <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="23" t="n">
+      <c r="N18" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23" t="n">
+      <c r="O18" s="23"/>
+      <c r="P18" s="23" t="n">
         <v>210</v>
       </c>
-      <c r="U18" s="23"/>
+      <c r="Q18" s="23"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="n">
@@ -5902,18 +5883,14 @@
         <v>4</v>
       </c>
       <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="39"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="39"/>
-      <c r="R19" s="23" t="n">
+      <c r="N19" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23" t="n">
+      <c r="O19" s="23"/>
+      <c r="P19" s="23" t="n">
         <v>231</v>
       </c>
-      <c r="U19" s="23"/>
+      <c r="Q19" s="23"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="n">
@@ -5939,18 +5916,14 @@
         <v>3</v>
       </c>
       <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="23" t="n">
+      <c r="N20" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23" t="n">
+      <c r="O20" s="23"/>
+      <c r="P20" s="23" t="n">
         <v>231</v>
       </c>
-      <c r="U20" s="23"/>
+      <c r="Q20" s="23"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="n">
@@ -5976,18 +5949,14 @@
         <v>3</v>
       </c>
       <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="39"/>
-      <c r="R21" s="23" t="n">
+      <c r="N21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23" t="n">
+      <c r="O21" s="23"/>
+      <c r="P21" s="23" t="n">
         <v>231</v>
       </c>
-      <c r="U21" s="23"/>
+      <c r="Q21" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="n">
@@ -6013,18 +5982,14 @@
         <v>3</v>
       </c>
       <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="23" t="n">
+      <c r="N22" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23" t="n">
+      <c r="O22" s="23"/>
+      <c r="P22" s="23" t="n">
         <v>171</v>
       </c>
-      <c r="U22" s="23"/>
+      <c r="Q22" s="23"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23"/>
@@ -6050,18 +6015,14 @@
         <v>3</v>
       </c>
       <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="23"/>
+      <c r="N23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="n">
@@ -6087,18 +6048,14 @@
         <v>3</v>
       </c>
       <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="23" t="n">
+      <c r="N24" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23" t="n">
+      <c r="O24" s="23"/>
+      <c r="P24" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="U24" s="23"/>
+      <c r="Q24" s="23"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="n">
@@ -6124,18 +6081,14 @@
         <v>3</v>
       </c>
       <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="23" t="n">
+      <c r="N25" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23" t="n">
+      <c r="O25" s="23"/>
+      <c r="P25" s="23" t="n">
         <v>210</v>
       </c>
-      <c r="U25" s="23"/>
+      <c r="Q25" s="23"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23"/>
@@ -6159,18 +6112,14 @@
         <v>2</v>
       </c>
       <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="39"/>
-      <c r="R26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="23"/>
+      <c r="N26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="23"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23"/>
@@ -6194,18 +6143,14 @@
         <v>2</v>
       </c>
       <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="23"/>
+      <c r="N27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="23"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23"/>
@@ -6229,18 +6174,14 @@
         <v>2</v>
       </c>
       <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="23"/>
+      <c r="N28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="23"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23"/>
@@ -6264,18 +6205,14 @@
         <v>2</v>
       </c>
       <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="23"/>
+      <c r="N29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="23"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23"/>
@@ -6299,18 +6236,14 @@
         <v>2</v>
       </c>
       <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="23"/>
+      <c r="N30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="23"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23"/>
@@ -6334,18 +6267,14 @@
         <v>2</v>
       </c>
       <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="23"/>
+      <c r="N31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="23"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23"/>
@@ -6369,18 +6298,14 @@
         <v>1</v>
       </c>
       <c r="M32" s="39"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="39"/>
-      <c r="Q32" s="39"/>
-      <c r="R32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="23"/>
-      <c r="T32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="23"/>
+      <c r="N32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23"/>
@@ -6404,18 +6329,14 @@
         <v>1</v>
       </c>
       <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="39"/>
-      <c r="Q33" s="39"/>
-      <c r="R33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="23"/>
+      <c r="N33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="23"/>
+      <c r="P33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="23"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23"/>
@@ -6439,18 +6360,14 @@
         <v>1</v>
       </c>
       <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="23"/>
-      <c r="T34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="23"/>
+      <c r="N34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23"/>
@@ -6474,18 +6391,14 @@
         <v>1</v>
       </c>
       <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="39"/>
-      <c r="R35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="23"/>
-      <c r="T35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="23"/>
+      <c r="N35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="23"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23"/>
@@ -6509,18 +6422,14 @@
         <v>1</v>
       </c>
       <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="23"/>
-      <c r="T36" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="23"/>
+      <c r="N36" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="23"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23"/>
@@ -6544,18 +6453,14 @@
         <v>1</v>
       </c>
       <c r="M37" s="39"/>
-      <c r="N37" s="39"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="39"/>
-      <c r="Q37" s="39"/>
-      <c r="R37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="23"/>
-      <c r="T37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="23"/>
+      <c r="N37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="23"/>
+      <c r="P37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="23"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23"/>
@@ -6571,16 +6476,12 @@
       <c r="K38" s="39"/>
       <c r="L38" s="39"/>
       <c r="M38" s="39"/>
-      <c r="N38" s="39"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="39"/>
-      <c r="Q38" s="39"/>
-      <c r="R38" s="23"/>
-      <c r="S38" s="23"/>
-      <c r="T38" s="23" t="n">
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="23" t="n">
         <v>12680</v>
       </c>
-      <c r="U38" s="40" t="n">
+      <c r="Q38" s="40" t="n">
         <v>11420</v>
       </c>
     </row>
@@ -6598,16 +6499,12 @@
       <c r="K39" s="39"/>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="23"/>
-      <c r="S39" s="23"/>
-      <c r="T39" s="23" t="n">
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="23" t="n">
         <v>1260</v>
       </c>
-      <c r="U39" s="23"/>
+      <c r="Q39" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/158/prob158.xlsx
+++ b/158/prob158.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
@@ -14,6 +14,12 @@
     <sheet name="seven" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="A" vbProcedure="false">Sheet5!$W$2</definedName>
+    <definedName function="false" hidden="false" name="B" vbProcedure="false">Sheet5!$W$3</definedName>
+    <definedName function="false" hidden="false" name="ll" vbProcedure="false">Sheet5!$H$3:$H$38</definedName>
+    <definedName function="false" hidden="false" name="rr" vbProcedure="false">Sheet5!$L$3:$L$38</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -24,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
   <si>
     <t xml:space="preserve">a</t>
   </si>
@@ -118,6 +124,18 @@
   <si>
     <t xml:space="preserve">Minimum #'s</t>
   </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
 </sst>
 </file>
 
@@ -196,7 +214,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -243,6 +261,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF000000"/>
         <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -296,7 +320,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -457,6 +481,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -470,6 +502,30 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -3083,7 +3139,7 @@
       </c>
       <c r="G4" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00025</v>
+        <v>0.00023</v>
       </c>
       <c r="H4" s="30" t="s">
         <v>21</v>
@@ -3099,14 +3155,14 @@
       </c>
       <c r="E5" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.608</v>
+        <v>0.562</v>
       </c>
       <c r="F5" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00023</v>
+        <v>0.00013</v>
       </c>
       <c r="H5" s="30" t="s">
         <v>21</v>
@@ -3122,7 +3178,7 @@
       </c>
       <c r="E6" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.441</v>
+        <v>0.482</v>
       </c>
       <c r="F6" s="33" t="n">
         <v>5</v>
@@ -3152,7 +3208,7 @@
       </c>
       <c r="G7" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00014</v>
+        <v>7E-005</v>
       </c>
       <c r="H7" s="30" t="s">
         <v>21</v>
@@ -3168,14 +3224,14 @@
       </c>
       <c r="E8" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.509</v>
+        <v>0.492</v>
       </c>
       <c r="F8" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00012</v>
+        <v>0.00022</v>
       </c>
       <c r="H8" s="33" t="n">
         <v>-2</v>
@@ -3191,14 +3247,14 @@
       </c>
       <c r="E9" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.551</v>
+        <v>0.524</v>
       </c>
       <c r="F9" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00021</v>
+        <v>9E-005</v>
       </c>
       <c r="H9" s="30" t="s">
         <v>21</v>
@@ -3214,14 +3270,14 @@
       </c>
       <c r="E10" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.492</v>
+        <v>0.61</v>
       </c>
       <c r="F10" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>9E-005</v>
+        <v>0.00013</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>21</v>
@@ -3237,14 +3293,14 @@
       </c>
       <c r="E11" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.445</v>
+        <v>0.571</v>
       </c>
       <c r="F11" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00016</v>
+        <v>8E-005</v>
       </c>
       <c r="H11" s="30" t="s">
         <v>21</v>
@@ -3276,7 +3332,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q58"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="11.79"/>
@@ -5271,21 +5327,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AK54"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="4.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="5.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="5.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="18" style="0" width="5.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="26" style="0" width="6.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A1" s="23"/>
+      <c r="B1" s="1"/>
       <c r="C1" s="23"/>
       <c r="D1" s="38"/>
       <c r="E1" s="39"/>
@@ -5293,93 +5348,189 @@
       <c r="G1" s="39"/>
       <c r="H1" s="38"/>
       <c r="I1" s="39"/>
-      <c r="J1" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="K1" s="39" t="n">
-        <v>1</v>
-      </c>
+      <c r="J1" s="38"/>
+      <c r="K1" s="39"/>
       <c r="L1" s="38"/>
       <c r="M1" s="39"/>
       <c r="N1" s="23"/>
       <c r="O1" s="23"/>
       <c r="P1" s="23"/>
       <c r="Q1" s="23"/>
+      <c r="Z1" s="0" t="n">
+        <f aca="false">COMBIN(AA1,AB1)</f>
+        <v>190</v>
+      </c>
+      <c r="AA1" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB1" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD1" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE1" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ1" s="0" t="n">
+        <f aca="false">Z1*AH1</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
+      <c r="A2" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="C2" s="23"/>
-      <c r="D2" s="39"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="F2" s="38"/>
       <c r="G2" s="39"/>
-      <c r="H2" s="39" t="n">
-        <v>6</v>
-      </c>
+      <c r="H2" s="38"/>
       <c r="I2" s="39"/>
-      <c r="J2" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39" t="n">
-        <v>6</v>
-      </c>
+      <c r="J2" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="38"/>
       <c r="M2" s="39"/>
       <c r="N2" s="23"/>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
+      <c r="V2" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="0" t="n">
+        <f aca="false">COMBIN(AA2,AB2)</f>
+        <v>190</v>
+      </c>
+      <c r="AA2" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB2" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF2" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH2" s="0" t="n">
+        <f aca="false">COMBIN(AF2,AG2)</f>
+        <v>3</v>
+      </c>
+      <c r="AJ2" s="0" t="n">
+        <f aca="false">Z2*AH2</f>
+        <v>570</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="C3" s="23" t="n">
-        <v>171</v>
-      </c>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="39"/>
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
       <c r="G3" s="39"/>
       <c r="H3" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="J3" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" s="39"/>
       <c r="L3" s="39" t="n">
         <v>6</v>
       </c>
       <c r="M3" s="39"/>
-      <c r="N3" s="23" t="n">
-        <v>6</v>
-      </c>
+      <c r="N3" s="23"/>
       <c r="O3" s="23"/>
-      <c r="P3" s="23" t="n">
-        <v>1026</v>
-      </c>
+      <c r="P3" s="23"/>
       <c r="Q3" s="23"/>
+      <c r="V3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="0" t="n">
+        <f aca="false">COMBIN(AA3,AB3)</f>
+        <v>190</v>
+      </c>
+      <c r="AA3" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB3" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH3" s="0" t="n">
+        <f aca="false">COMBIN(AF3,AG3)</f>
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="0" t="n">
+        <f aca="false">Z3*AH3</f>
+        <v>570</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="23" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="39"/>
       <c r="F4" s="39"/>
       <c r="G4" s="39"/>
       <c r="H4" s="39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="39"/>
       <c r="J4" s="39"/>
@@ -5393,26 +5544,59 @@
       </c>
       <c r="O4" s="23"/>
       <c r="P4" s="23" t="n">
+        <v>1026</v>
+      </c>
+      <c r="Q4" s="23"/>
+      <c r="Z4" s="0" t="n">
+        <f aca="false">COMBIN(AA4,AB4)</f>
+        <v>190</v>
+      </c>
+      <c r="AA4" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB4" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF4" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG4" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="0" t="n">
+        <f aca="false">COMBIN(AF4,AG4)</f>
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="0" t="n">
+        <f aca="false">Z4*AH4</f>
         <v>1140</v>
       </c>
-      <c r="Q4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D5" s="39"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="39"/>
       <c r="H5" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="39"/>
       <c r="J5" s="39"/>
@@ -5426,26 +5610,54 @@
       </c>
       <c r="O5" s="23"/>
       <c r="P5" s="23" t="n">
-        <v>1260</v>
+        <v>1140</v>
       </c>
       <c r="Q5" s="23"/>
+      <c r="Z5" s="0" t="n">
+        <f aca="false">COMBIN(AA5,AB5)</f>
+        <v>190</v>
+      </c>
+      <c r="AA5" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" s="40"/>
+      <c r="AG5" s="40"/>
+      <c r="AH5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="0" t="n">
+        <f aca="false">Z5*AH5</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
       <c r="G6" s="39"/>
       <c r="H6" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="39"/>
       <c r="J6" s="39"/>
@@ -5459,9 +5671,42 @@
       </c>
       <c r="O6" s="23"/>
       <c r="P6" s="23" t="n">
-        <v>1386</v>
+        <v>1260</v>
       </c>
       <c r="Q6" s="23"/>
+      <c r="Z6" s="0" t="n">
+        <f aca="false">COMBIN(AA6,AB6)</f>
+        <v>190</v>
+      </c>
+      <c r="AA6" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" s="0" t="n">
+        <f aca="false">COMBIN(AF6,AG6)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="0" t="n">
+        <f aca="false">Z6*AH6</f>
+        <v>190</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="n">
@@ -5470,15 +5715,15 @@
       <c r="B7" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="C7" s="23" t="n">
-        <v>231</v>
+      <c r="C7" s="23" t="s">
+        <v>33</v>
       </c>
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
       <c r="G7" s="39"/>
       <c r="H7" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="39"/>
       <c r="J7" s="39"/>
@@ -5495,29 +5740,62 @@
         <v>1386</v>
       </c>
       <c r="Q7" s="23"/>
+      <c r="Z7" s="0" t="n">
+        <f aca="false">COMBIN(AA7,AB7)</f>
+        <v>190</v>
+      </c>
+      <c r="AA7" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="0" t="n">
+        <f aca="false">COMBIN(AF7,AG7)</f>
+        <v>3</v>
+      </c>
+      <c r="AJ7" s="0" t="n">
+        <f aca="false">Z7*AH7</f>
+        <v>570</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8" s="23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="D8" s="39"/>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
       <c r="G8" s="39"/>
       <c r="H8" s="39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I8" s="39"/>
       <c r="J8" s="39"/>
       <c r="K8" s="39"/>
       <c r="L8" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" s="39"/>
       <c r="N8" s="23" t="n">
@@ -5525,12 +5803,47 @@
       </c>
       <c r="O8" s="23"/>
       <c r="P8" s="23" t="n">
+        <v>1386</v>
+      </c>
+      <c r="Q8" s="23"/>
+      <c r="Z8" s="0" t="n">
+        <f aca="false">COMBIN(AA8,AB8)</f>
+        <v>171</v>
+      </c>
+      <c r="AA8" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF8" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="0" t="n">
+        <f aca="false">COMBIN(AF8,AG8)</f>
+        <v>6</v>
+      </c>
+      <c r="AJ8" s="0" t="n">
+        <f aca="false">Z8*AH8</f>
         <v>1026</v>
       </c>
-      <c r="Q8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23"/>
+      <c r="A9" s="23" t="n">
+        <v>0</v>
+      </c>
       <c r="B9" s="23" t="n">
         <v>19</v>
       </c>
@@ -5542,75 +5855,139 @@
       <c r="F9" s="39"/>
       <c r="G9" s="39"/>
       <c r="H9" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="39"/>
-      <c r="J9" s="39" t="n">
-        <v>0</v>
-      </c>
+      <c r="J9" s="39"/>
       <c r="K9" s="39"/>
       <c r="L9" s="39" t="n">
         <v>5</v>
       </c>
       <c r="M9" s="39"/>
       <c r="N9" s="23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O9" s="23"/>
       <c r="P9" s="23" t="n">
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="Q9" s="23"/>
+      <c r="Z9" s="0" t="n">
+        <f aca="false">COMBIN(AA9,AB9)</f>
+        <v>190</v>
+      </c>
+      <c r="AA9" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE9" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" s="0" t="n">
+        <f aca="false">COMBIN(AF9,AG9)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="0" t="n">
+        <f aca="false">Z9*AH9</f>
+        <v>190</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="n">
-        <v>1</v>
-      </c>
+      <c r="A10" s="23"/>
       <c r="B10" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D10" s="39"/>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
+      <c r="J10" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="K10" s="39"/>
       <c r="L10" s="39" t="n">
         <v>5</v>
       </c>
       <c r="M10" s="39"/>
       <c r="N10" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="23"/>
+      <c r="Z10" s="0" t="n">
+        <f aca="false">COMBIN(AA10,AB10)</f>
+        <v>190</v>
+      </c>
+      <c r="AA10" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB10" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE10" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH10" s="0" t="n">
+        <f aca="false">COMBIN(AF10,AG10)</f>
+        <v>3</v>
+      </c>
+      <c r="AJ10" s="0" t="n">
+        <f aca="false">Z10*AH10</f>
         <v>570</v>
       </c>
-      <c r="Q10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D11" s="39"/>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="39"/>
       <c r="J11" s="39"/>
@@ -5624,26 +6001,59 @@
       </c>
       <c r="O11" s="23"/>
       <c r="P11" s="23" t="n">
-        <v>630</v>
+        <v>570</v>
       </c>
       <c r="Q11" s="23"/>
+      <c r="Z11" s="0" t="n">
+        <f aca="false">COMBIN(AA11,AB11)</f>
+        <v>153</v>
+      </c>
+      <c r="AA11" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB11" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD11" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE11" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF11" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG11" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="0" t="n">
+        <f aca="false">COMBIN(AF11,AG11)</f>
+        <v>6</v>
+      </c>
+      <c r="AJ11" s="0" t="n">
+        <f aca="false">Z11*AH11</f>
+        <v>918</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="23" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="39"/>
       <c r="H12" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="39"/>
       <c r="J12" s="39"/>
@@ -5657,9 +6067,38 @@
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="23" t="n">
-        <v>693</v>
+        <v>630</v>
       </c>
       <c r="Q12" s="23"/>
+      <c r="Z12" s="0" t="n">
+        <f aca="false">COMBIN(AA12,AB12)</f>
+        <v>190</v>
+      </c>
+      <c r="AA12" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB12" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD12" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF12" s="40"/>
+      <c r="AG12" s="40"/>
+      <c r="AH12" s="0" t="n">
+        <f aca="false">COMBIN(AF12,AG12)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="0" t="n">
+        <f aca="false">Z12*AH12</f>
+        <v>190</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="n">
@@ -5676,7 +6115,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="39"/>
       <c r="H13" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="39"/>
       <c r="J13" s="39"/>
@@ -5693,6 +6132,39 @@
         <v>693</v>
       </c>
       <c r="Q13" s="23"/>
+      <c r="Z13" s="0" t="n">
+        <f aca="false">COMBIN(AA13,AB13)</f>
+        <v>190</v>
+      </c>
+      <c r="AA13" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB13" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD13" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE13" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" s="0" t="n">
+        <f aca="false">COMBIN(AF13,AG13)</f>
+        <v>3</v>
+      </c>
+      <c r="AJ13" s="0" t="n">
+        <f aca="false">Z13*AH13</f>
+        <v>570</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="n">
@@ -5709,13 +6181,13 @@
       <c r="F14" s="39"/>
       <c r="G14" s="39"/>
       <c r="H14" s="39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I14" s="39"/>
       <c r="J14" s="39"/>
       <c r="K14" s="39"/>
       <c r="L14" s="39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M14" s="39"/>
       <c r="N14" s="23" t="n">
@@ -5726,23 +6198,56 @@
         <v>693</v>
       </c>
       <c r="Q14" s="23"/>
+      <c r="Z14" s="0" t="n">
+        <f aca="false">COMBIN(AA14,AB14)</f>
+        <v>153</v>
+      </c>
+      <c r="AA14" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB14" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD14" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE14" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF14" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="0" t="n">
+        <f aca="false">COMBIN(AF14,AG14)</f>
+        <v>6</v>
+      </c>
+      <c r="AJ14" s="0" t="n">
+        <f aca="false">Z14*AH14</f>
+        <v>918</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" s="23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
       <c r="H15" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="39"/>
       <c r="J15" s="39"/>
@@ -5756,12 +6261,43 @@
       </c>
       <c r="O15" s="23"/>
       <c r="P15" s="23" t="n">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="Q15" s="23"/>
+      <c r="Z15" s="0" t="n">
+        <f aca="false">COMBIN(AA15,AB15)</f>
+        <v>190</v>
+      </c>
+      <c r="AA15" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB15" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE15" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="0" t="n">
+        <f aca="false">COMBIN(AF15,AG15)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="0" t="n">
+        <f aca="false">Z15*AH15</f>
+        <v>190</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23"/>
+      <c r="A16" s="23" t="n">
+        <v>0</v>
+      </c>
       <c r="B16" s="23" t="n">
         <v>19</v>
       </c>
@@ -5773,75 +6309,139 @@
       <c r="F16" s="39"/>
       <c r="G16" s="39"/>
       <c r="H16" s="39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="39" t="n">
-        <v>0</v>
-      </c>
+      <c r="J16" s="39"/>
       <c r="K16" s="39"/>
       <c r="L16" s="39" t="n">
         <v>4</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" s="23"/>
       <c r="P16" s="23" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="Q16" s="23"/>
+      <c r="Z16" s="0" t="n">
+        <f aca="false">COMBIN(AA16,AB16)</f>
+        <v>171</v>
+      </c>
+      <c r="AA16" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB16" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE16" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF16" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" s="0" t="n">
+        <f aca="false">COMBIN(AF16,AG16)</f>
+        <v>3</v>
+      </c>
+      <c r="AJ16" s="0" t="n">
+        <f aca="false">Z16*AH16</f>
+        <v>513</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="n">
-        <v>1</v>
-      </c>
+      <c r="A17" s="23"/>
       <c r="B17" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="39"/>
       <c r="H17" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
+      <c r="J17" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="K17" s="39"/>
       <c r="L17" s="39" t="n">
         <v>4</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="23" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="23"/>
+      <c r="Z17" s="0" t="n">
+        <f aca="false">COMBIN(AA17,AB17)</f>
+        <v>153</v>
+      </c>
+      <c r="AA17" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB17" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE17" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF17" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" s="0" t="n">
+        <f aca="false">COMBIN(AF17,AG17)</f>
+        <v>6</v>
+      </c>
+      <c r="AJ17" s="0" t="n">
+        <f aca="false">Z17*AH17</f>
+        <v>918</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
       <c r="F18" s="39"/>
       <c r="G18" s="39"/>
       <c r="H18" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="39"/>
       <c r="J18" s="39"/>
@@ -5855,26 +6455,55 @@
       </c>
       <c r="O18" s="23"/>
       <c r="P18" s="23" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="Q18" s="23"/>
+      <c r="Z18" s="0" t="n">
+        <f aca="false">COMBIN(AA18,AB18)</f>
+        <v>153</v>
+      </c>
+      <c r="AA18" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB18" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD18" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE18" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF18" s="40"/>
+      <c r="AG18" s="40"/>
+      <c r="AH18" s="0" t="n">
+        <f aca="false">COMBIN(AF18,AG18)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="0" t="n">
+        <f aca="false">Z18*AH18</f>
+        <v>153</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" s="23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="D19" s="39"/>
       <c r="E19" s="39"/>
       <c r="F19" s="39"/>
       <c r="G19" s="39"/>
       <c r="H19" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="39"/>
       <c r="J19" s="39"/>
@@ -5888,9 +6517,42 @@
       </c>
       <c r="O19" s="23"/>
       <c r="P19" s="23" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="Q19" s="23"/>
+      <c r="Z19" s="0" t="n">
+        <f aca="false">COMBIN(AA19,AB19)</f>
+        <v>153</v>
+      </c>
+      <c r="AA19" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB19" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC19" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD19" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE19" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF19" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH19" s="0" t="n">
+        <f aca="false">COMBIN(AF19,AG19)</f>
+        <v>3</v>
+      </c>
+      <c r="AJ19" s="0" t="n">
+        <f aca="false">Z19*AH19</f>
+        <v>459</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="n">
@@ -5907,13 +6569,13 @@
       <c r="F20" s="39"/>
       <c r="G20" s="39"/>
       <c r="H20" s="39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I20" s="39"/>
       <c r="J20" s="39"/>
       <c r="K20" s="39"/>
       <c r="L20" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20" s="39"/>
       <c r="N20" s="23" t="n">
@@ -5924,6 +6586,39 @@
         <v>231</v>
       </c>
       <c r="Q20" s="23"/>
+      <c r="Z20" s="0" t="n">
+        <f aca="false">COMBIN(AA20,AB20)</f>
+        <v>153</v>
+      </c>
+      <c r="AA20" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB20" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC20" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD20" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE20" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="0" t="n">
+        <f aca="false">COMBIN(AF20,AG20)</f>
+        <v>6</v>
+      </c>
+      <c r="AJ20" s="0" t="n">
+        <f aca="false">Z20*AH20</f>
+        <v>918</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="n">
@@ -5940,7 +6635,7 @@
       <c r="F21" s="39"/>
       <c r="G21" s="39"/>
       <c r="H21" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="39"/>
       <c r="J21" s="39"/>
@@ -5957,23 +6652,36 @@
         <v>231</v>
       </c>
       <c r="Q21" s="23"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="40"/>
+      <c r="AC21" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD21" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE21" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF21" s="40"/>
+      <c r="AG21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B22" s="23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="D22" s="39"/>
       <c r="E22" s="39"/>
       <c r="F22" s="39"/>
       <c r="G22" s="39"/>
       <c r="H22" s="39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="39"/>
       <c r="J22" s="39"/>
@@ -5987,12 +6695,28 @@
       </c>
       <c r="O22" s="23"/>
       <c r="P22" s="23" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="Q22" s="23"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41"/>
+      <c r="AC22" s="41"/>
+      <c r="AD22" s="41"/>
+      <c r="AE22" s="41"/>
+      <c r="AF22" s="41"/>
+      <c r="AG22" s="41"/>
+      <c r="AJ22" s="0" t="n">
+        <f aca="false">SUM(AJ2:AJ21)</f>
+        <v>10573</v>
+      </c>
+      <c r="AK22" s="21" t="n">
+        <v>11420</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23"/>
+      <c r="A23" s="23" t="n">
+        <v>0</v>
+      </c>
       <c r="B23" s="23" t="n">
         <v>19</v>
       </c>
@@ -6004,75 +6728,91 @@
       <c r="F23" s="39"/>
       <c r="G23" s="39"/>
       <c r="H23" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="39"/>
-      <c r="J23" s="39" t="n">
-        <v>0</v>
-      </c>
+      <c r="J23" s="39"/>
       <c r="K23" s="39"/>
       <c r="L23" s="39" t="n">
         <v>3</v>
       </c>
       <c r="M23" s="39"/>
       <c r="N23" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="23"/>
       <c r="P23" s="23" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="Q23" s="23"/>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="41"/>
+      <c r="AC23" s="41"/>
+      <c r="AD23" s="41"/>
+      <c r="AE23" s="41"/>
+      <c r="AF23" s="41"/>
+      <c r="AG23" s="41"/>
+      <c r="AJ23" s="0" t="n">
+        <f aca="false">AK22-AJ22</f>
+        <v>847</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23" t="n">
-        <v>1</v>
-      </c>
+      <c r="A24" s="23"/>
       <c r="B24" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39"/>
       <c r="H24" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
+      <c r="J24" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="K24" s="39"/>
       <c r="L24" s="39" t="n">
         <v>3</v>
       </c>
       <c r="M24" s="39"/>
       <c r="N24" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="23"/>
       <c r="P24" s="23" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="23"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="41"/>
+      <c r="AC24" s="41"/>
+      <c r="AD24" s="41"/>
+      <c r="AE24" s="41"/>
+      <c r="AF24" s="41"/>
+      <c r="AG24" s="41"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
       <c r="H25" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="39"/>
       <c r="J25" s="39"/>
@@ -6086,55 +6826,71 @@
       </c>
       <c r="O25" s="23"/>
       <c r="P25" s="23" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q25" s="23"/>
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="41"/>
+      <c r="AD25" s="41"/>
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="41"/>
+      <c r="AG25" s="41"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="23" t="n">
         <v>210</v>
-      </c>
-      <c r="Q25" s="23"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="C26" s="23" t="n">
-        <v>136</v>
       </c>
       <c r="D26" s="39"/>
       <c r="E26" s="39"/>
       <c r="F26" s="39"/>
       <c r="G26" s="39"/>
       <c r="H26" s="39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I26" s="39"/>
       <c r="J26" s="39"/>
       <c r="K26" s="39"/>
       <c r="L26" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M26" s="39"/>
       <c r="N26" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="23"/>
       <c r="P26" s="23" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="Q26" s="23"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="41"/>
+      <c r="AC26" s="41"/>
+      <c r="AD26" s="41"/>
+      <c r="AE26" s="41"/>
+      <c r="AF26" s="41"/>
+      <c r="AG26" s="41"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23"/>
       <c r="B27" s="23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="23" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D27" s="39"/>
       <c r="E27" s="39"/>
       <c r="F27" s="39"/>
       <c r="G27" s="39"/>
       <c r="H27" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="39"/>
       <c r="J27" s="39"/>
@@ -6151,21 +6907,28 @@
         <v>0</v>
       </c>
       <c r="Q27" s="23"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="41"/>
+      <c r="AE27" s="41"/>
+      <c r="AF27" s="41"/>
+      <c r="AG27" s="41"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23"/>
       <c r="B28" s="23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="23" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D28" s="39"/>
       <c r="E28" s="39"/>
       <c r="F28" s="39"/>
       <c r="G28" s="39"/>
       <c r="H28" s="39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" s="39"/>
       <c r="J28" s="39"/>
@@ -6186,17 +6949,17 @@
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23"/>
       <c r="B29" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="39"/>
       <c r="H29" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="39"/>
       <c r="J29" s="39"/>
@@ -6217,17 +6980,17 @@
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23"/>
       <c r="B30" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" s="23" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="39"/>
       <c r="G30" s="39"/>
       <c r="H30" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="39"/>
       <c r="J30" s="39"/>
@@ -6258,7 +7021,7 @@
       <c r="F31" s="39"/>
       <c r="G31" s="39"/>
       <c r="H31" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="39"/>
@@ -6279,23 +7042,23 @@
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23"/>
       <c r="B32" s="23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C32" s="23" t="n">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="D32" s="39"/>
       <c r="E32" s="39"/>
       <c r="F32" s="39"/>
       <c r="G32" s="39"/>
       <c r="H32" s="39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I32" s="39"/>
       <c r="J32" s="39"/>
       <c r="K32" s="39"/>
       <c r="L32" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="39"/>
       <c r="N32" s="23" t="n">
@@ -6310,17 +7073,17 @@
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23"/>
       <c r="B33" s="23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" s="23" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D33" s="39"/>
       <c r="E33" s="39"/>
       <c r="F33" s="39"/>
       <c r="G33" s="39"/>
       <c r="H33" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="39"/>
       <c r="J33" s="39"/>
@@ -6341,17 +7104,17 @@
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23"/>
       <c r="B34" s="23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" s="23" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D34" s="39"/>
       <c r="E34" s="39"/>
       <c r="F34" s="39"/>
       <c r="G34" s="39"/>
       <c r="H34" s="39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="39"/>
       <c r="J34" s="39"/>
@@ -6372,17 +7135,17 @@
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23"/>
       <c r="B35" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" s="23" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D35" s="39"/>
       <c r="E35" s="39"/>
       <c r="F35" s="39"/>
       <c r="G35" s="39"/>
       <c r="H35" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="39"/>
       <c r="J35" s="39"/>
@@ -6403,17 +7166,17 @@
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23"/>
       <c r="B36" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" s="23" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D36" s="39"/>
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
       <c r="G36" s="39"/>
       <c r="H36" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="39"/>
       <c r="J36" s="39"/>
@@ -6434,17 +7197,17 @@
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23"/>
       <c r="B37" s="23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C37" s="23" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="D37" s="39"/>
       <c r="E37" s="39"/>
       <c r="F37" s="39"/>
       <c r="G37" s="39"/>
       <c r="H37" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="39"/>
       <c r="J37" s="39"/>
@@ -6464,26 +7227,34 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
+      <c r="B38" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>231</v>
+      </c>
       <c r="D38" s="39"/>
       <c r="E38" s="39"/>
       <c r="F38" s="39"/>
       <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
+      <c r="H38" s="39" t="n">
+        <v>1</v>
+      </c>
       <c r="I38" s="39"/>
       <c r="J38" s="39"/>
       <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
+      <c r="L38" s="39" t="n">
+        <v>1</v>
+      </c>
       <c r="M38" s="39"/>
-      <c r="N38" s="23"/>
+      <c r="N38" s="23" t="n">
+        <v>0</v>
+      </c>
       <c r="O38" s="23"/>
       <c r="P38" s="23" t="n">
-        <v>12680</v>
-      </c>
-      <c r="Q38" s="40" t="n">
-        <v>11420</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="23"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23"/>
@@ -6502,9 +7273,37 @@
       <c r="N39" s="23"/>
       <c r="O39" s="23"/>
       <c r="P39" s="23" t="n">
+        <v>12680</v>
+      </c>
+      <c r="Q39" s="42" t="n">
+        <v>11420</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23" t="n">
         <v>1260</v>
       </c>
-      <c r="Q39" s="23"/>
+      <c r="Q40" s="23"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AH54" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/158/prob158.xlsx
+++ b/158/prob158.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
@@ -13,6 +13,7 @@
     <sheet name="Receiver Timing" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="seven" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="A" vbProcedure="false">Sheet5!$W$2</definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="36">
   <si>
     <t xml:space="preserve">a</t>
   </si>
@@ -135,6 +136,9 @@
   </si>
   <si>
     <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M= 4, K = 7, A = 3, B = 3, L = 7</t>
   </si>
 </sst>
 </file>
@@ -3139,7 +3143,7 @@
       </c>
       <c r="G4" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00023</v>
+        <v>0.00021</v>
       </c>
       <c r="H4" s="30" t="s">
         <v>21</v>
@@ -3155,14 +3159,14 @@
       </c>
       <c r="E5" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.562</v>
+        <v>0.51</v>
       </c>
       <c r="F5" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00013</v>
+        <v>5E-005</v>
       </c>
       <c r="H5" s="30" t="s">
         <v>21</v>
@@ -3178,14 +3182,14 @@
       </c>
       <c r="E6" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.482</v>
+        <v>0.553</v>
       </c>
       <c r="F6" s="33" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00024</v>
+        <v>0.00023</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>21</v>
@@ -3208,7 +3212,7 @@
       </c>
       <c r="G7" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>7E-005</v>
+        <v>0.00015</v>
       </c>
       <c r="H7" s="30" t="s">
         <v>21</v>
@@ -3224,14 +3228,14 @@
       </c>
       <c r="E8" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.492</v>
+        <v>0.423</v>
       </c>
       <c r="F8" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00022</v>
+        <v>0.00023</v>
       </c>
       <c r="H8" s="33" t="n">
         <v>-2</v>
@@ -3247,14 +3251,14 @@
       </c>
       <c r="E9" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.524</v>
+        <v>0.49</v>
       </c>
       <c r="F9" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>9E-005</v>
+        <v>0.00025</v>
       </c>
       <c r="H9" s="30" t="s">
         <v>21</v>
@@ -3270,14 +3274,14 @@
       </c>
       <c r="E10" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.61</v>
+        <v>0.544</v>
       </c>
       <c r="F10" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00013</v>
+        <v>9E-005</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>21</v>
@@ -3293,14 +3297,14 @@
       </c>
       <c r="E11" s="32" t="n">
         <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.571</v>
+        <v>0.603</v>
       </c>
       <c r="F11" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="30" t="n">
         <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>8E-005</v>
+        <v>0.0002</v>
       </c>
       <c r="H11" s="30" t="s">
         <v>21</v>
@@ -5335,7 +5339,6 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="5.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="18" style="0" width="5.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="26" style="0" width="6.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7314,4 +7317,359 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/158/prob158.xlsx
+++ b/158/prob158.xlsx
@@ -8,12 +8,12 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Receiver Timing" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="seven" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Sheet6" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Receiver Timing" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="seven" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="A" vbProcedure="false">Sheet5!$W$2</definedName>
@@ -324,176 +324,172 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -506,30 +502,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -593,8 +565,114 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1153,7 +1231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1161,153 +1239,153 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="F1" s="0" t="n">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="F1" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="L1" s="0" t="n">
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="L1" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="8" t="s">
+      <c r="C2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="9" t="n">
+      <c r="H2" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" s="11" t="n">
+      <c r="N2" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" s="11" t="n">
+      <c r="Q2" s="12" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15" t="n">
+      <c r="C3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="17" t="n">
+      <c r="H3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
+      <c r="N3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <f aca="false">(B4-2)*COMBIN(B4-1, 1)</f>
         <v>0</v>
       </c>
-      <c r="B4" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="14" t="n">
+      <c r="B4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="G4" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="16" t="n">
+      <c r="G4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17" t="n">
         <v>276</v>
       </c>
-      <c r="M4" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="18" t="n">
+      <c r="M4" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="19" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -1316,50 +1394,50 @@
         <f aca="false">(B5-2)*COMBIN(B5-1, 1)</f>
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="14" t="n">
+      <c r="B5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="15" t="n">
         <v>47</v>
       </c>
       <c r="F5" s="1" t="n">
         <f aca="false">(G5-3)*COMBIN(G5-1, 2)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="9" t="n">
+      <c r="G5" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="17" t="n">
         <v>529</v>
       </c>
-      <c r="M5" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="11" t="n">
+      <c r="M5" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="12" t="n">
         <v>506</v>
       </c>
-      <c r="Q5" s="18" t="n">
+      <c r="Q5" s="19" t="n">
         <v>3795</v>
       </c>
-      <c r="V5" s="20" t="n">
+      <c r="V5" s="21" t="n">
         <v>529</v>
       </c>
-      <c r="W5" s="20" t="n">
+      <c r="W5" s="21" t="n">
         <f aca="false">V5-P5</f>
         <v>23</v>
       </c>
@@ -1369,61 +1447,61 @@
         <f aca="false">(B6-2)*COMBIN(B6-1, 1)</f>
         <v>6</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>69</v>
       </c>
       <c r="F6" s="1" t="n">
         <f aca="false">(G6-3)*COMBIN(G6-1, 2)</f>
         <v>3</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="9" t="n">
+      <c r="H6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="10" t="n">
         <v>135</v>
       </c>
-      <c r="J6" s="16" t="n">
+      <c r="J6" s="17" t="n">
         <v>760</v>
       </c>
       <c r="L6" s="1" t="n">
         <f aca="false">(M6-4)*COMBIN(M6-1, 3)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="N6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="19" t="n">
+      <c r="N6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="12" t="n">
         <v>1452</v>
       </c>
-      <c r="Q6" s="18" t="n">
+      <c r="Q6" s="19" t="n">
         <v>5335</v>
       </c>
-      <c r="S6" s="21" t="n">
+      <c r="S6" s="22" t="n">
         <v>69</v>
       </c>
-      <c r="T6" s="21" t="n">
+      <c r="T6" s="22" t="n">
         <f aca="false">S6-O6</f>
         <v>3</v>
       </c>
-      <c r="V6" s="20" t="n">
+      <c r="V6" s="21" t="n">
         <v>1520</v>
       </c>
-      <c r="W6" s="20" t="n">
+      <c r="W6" s="21" t="n">
         <f aca="false">V6-P6</f>
         <v>68</v>
       </c>
@@ -1433,61 +1511,61 @@
         <f aca="false">(B7-2)*COMBIN(B7-1, 1)</f>
         <v>12</v>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>90</v>
       </c>
       <c r="F7" s="1" t="n">
         <f aca="false">(G7-3)*COMBIN(G7-1, 2)</f>
         <v>12</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10" t="n">
         <v>264</v>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="17" t="n">
         <v>970</v>
       </c>
       <c r="L7" s="1" t="n">
         <f aca="false">(M7-4)*COMBIN(M7-1, 3)</f>
         <v>4</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="18" t="n">
+      <c r="N7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O7" s="19" t="n">
+      <c r="O7" s="20" t="n">
         <v>258</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="12" t="n">
         <v>2776</v>
       </c>
-      <c r="Q7" s="18" t="n">
+      <c r="Q7" s="19" t="n">
         <v>6665</v>
       </c>
-      <c r="S7" s="21" t="n">
+      <c r="S7" s="22" t="n">
         <v>270</v>
       </c>
-      <c r="T7" s="21" t="n">
+      <c r="T7" s="22" t="n">
         <f aca="false">S7-O7</f>
         <v>12</v>
       </c>
-      <c r="V7" s="20" t="n">
+      <c r="V7" s="21" t="n">
         <v>2910</v>
       </c>
-      <c r="W7" s="20" t="n">
+      <c r="W7" s="21" t="n">
         <f aca="false">V7-P7</f>
         <v>134</v>
       </c>
@@ -1497,61 +1575,61 @@
         <f aca="false">(B8-2)*COMBIN(B8-1, 1)</f>
         <v>20</v>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>110</v>
       </c>
       <c r="F8" s="1" t="n">
         <f aca="false">(G8-3)*COMBIN(G8-1, 2)</f>
         <v>30</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="10" t="n">
         <v>430</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="17" t="n">
         <v>1160</v>
       </c>
       <c r="L8" s="1" t="n">
         <f aca="false">(M8-4)*COMBIN(M8-1, 3)</f>
         <v>20</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N8" s="18" t="n">
+      <c r="N8" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="O8" s="19" t="n">
+      <c r="O8" s="20" t="n">
         <v>630</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" s="12" t="n">
         <v>4420</v>
       </c>
-      <c r="Q8" s="18" t="n">
+      <c r="Q8" s="19" t="n">
         <v>7805</v>
       </c>
-      <c r="S8" s="21" t="n">
+      <c r="S8" s="22" t="n">
         <v>660</v>
       </c>
-      <c r="T8" s="21" t="n">
+      <c r="T8" s="22" t="n">
         <f aca="false">S8-O8</f>
         <v>30</v>
       </c>
-      <c r="V8" s="20" t="n">
+      <c r="V8" s="21" t="n">
         <v>4640</v>
       </c>
-      <c r="W8" s="20" t="n">
+      <c r="W8" s="21" t="n">
         <f aca="false">V8-P8</f>
         <v>220</v>
       </c>
@@ -1561,61 +1639,61 @@
         <f aca="false">(B9-2)*COMBIN(B9-1, 1)</f>
         <v>30</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>129</v>
       </c>
       <c r="F9" s="1" t="n">
         <f aca="false">(G9-3)*COMBIN(G9-1, 2)</f>
         <v>60</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="10" t="n">
         <v>630</v>
       </c>
-      <c r="J9" s="16" t="n">
+      <c r="J9" s="17" t="n">
         <v>1331</v>
       </c>
       <c r="L9" s="1" t="n">
         <f aca="false">(M9-4)*COMBIN(M9-1, 3)</f>
         <v>60</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="N9" s="18" t="n">
+      <c r="N9" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="O9" s="19" t="n">
+      <c r="O9" s="20" t="n">
         <v>1230</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="12" t="n">
         <v>6330</v>
       </c>
-      <c r="Q9" s="18" t="n">
+      <c r="Q9" s="19" t="n">
         <v>8774</v>
       </c>
-      <c r="S9" s="21" t="n">
+      <c r="S9" s="22" t="n">
         <v>1290</v>
       </c>
-      <c r="T9" s="21" t="n">
+      <c r="T9" s="22" t="n">
         <f aca="false">S9-O9</f>
         <v>60</v>
       </c>
-      <c r="V9" s="20" t="n">
+      <c r="V9" s="21" t="n">
         <v>6655</v>
       </c>
-      <c r="W9" s="20" t="n">
+      <c r="W9" s="21" t="n">
         <f aca="false">V9-P9</f>
         <v>325</v>
       </c>
@@ -1625,54 +1703,54 @@
         <f aca="false">(B10-2)*COMBIN(B10-1, 1)</f>
         <v>42</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>147</v>
       </c>
       <c r="F10" s="1" t="n">
         <f aca="false">(G10-3)*COMBIN(G10-1, 2)</f>
         <v>105</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="17" t="n">
         <v>105</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="10" t="n">
         <v>861</v>
       </c>
-      <c r="J10" s="16" t="n">
+      <c r="J10" s="17" t="n">
         <v>1484</v>
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">(M10-4)*COMBIN(M10-1, 3)</f>
         <v>140</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="N10" s="18" t="n">
+      <c r="N10" s="19" t="n">
         <v>140</v>
       </c>
-      <c r="O10" s="19" t="n">
+      <c r="O10" s="20" t="n">
         <v>2100</v>
       </c>
-      <c r="P10" s="11" t="n">
+      <c r="P10" s="12" t="n">
         <v>8456</v>
       </c>
-      <c r="Q10" s="18" t="n">
+      <c r="Q10" s="19" t="n">
         <v>9590</v>
       </c>
-      <c r="S10" s="21" t="n">
+      <c r="S10" s="22" t="n">
         <v>2205</v>
       </c>
-      <c r="T10" s="21" t="n">
+      <c r="T10" s="22" t="n">
         <f aca="false">S10-O10</f>
         <v>105</v>
       </c>
@@ -1682,54 +1760,54 @@
         <f aca="false">(B11-2)*COMBIN(B11-1, 1)</f>
         <v>56</v>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>164</v>
       </c>
       <c r="F11" s="1" t="n">
         <f aca="false">(G11-3)*COMBIN(G11-1, 2)</f>
         <v>168</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="17" t="n">
         <v>168</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="10" t="n">
         <v>1120</v>
       </c>
-      <c r="J11" s="16" t="n">
+      <c r="J11" s="17" t="n">
         <v>1620</v>
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">(M11-4)*COMBIN(M11-1, 3)</f>
         <v>280</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="N11" s="18" t="n">
+      <c r="N11" s="19" t="n">
         <v>280</v>
       </c>
-      <c r="O11" s="19" t="n">
+      <c r="O11" s="20" t="n">
         <v>3276</v>
       </c>
-      <c r="P11" s="11" t="n">
+      <c r="P11" s="12" t="n">
         <v>10752</v>
       </c>
-      <c r="Q11" s="18" t="n">
+      <c r="Q11" s="19" t="n">
         <v>10270</v>
       </c>
-      <c r="S11" s="21" t="n">
+      <c r="S11" s="22" t="n">
         <v>3444</v>
       </c>
-      <c r="T11" s="21" t="n">
+      <c r="T11" s="22" t="n">
         <f aca="false">S11-O11</f>
         <v>168</v>
       </c>
@@ -1739,48 +1817,48 @@
         <f aca="false">(B12-2)*COMBIN(B12-1, 1)</f>
         <v>72</v>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <v>72</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>180</v>
       </c>
       <c r="F12" s="1" t="n">
         <f aca="false">(G12-3)*COMBIN(G12-1, 2)</f>
         <v>252</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="17" t="n">
         <v>252</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="10" t="n">
         <v>1404</v>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="17" t="n">
         <v>1740</v>
       </c>
       <c r="L12" s="1" t="n">
         <f aca="false">(M12-4)*COMBIN(M12-1, 3)</f>
         <v>504</v>
       </c>
-      <c r="M12" s="17" t="n">
+      <c r="M12" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="N12" s="18" t="n">
+      <c r="N12" s="19" t="n">
         <v>504</v>
       </c>
-      <c r="O12" s="19" t="n">
+      <c r="O12" s="20" t="n">
         <v>4788</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="12" t="n">
         <v>13176</v>
       </c>
-      <c r="Q12" s="18" t="n">
+      <c r="Q12" s="19" t="n">
         <v>10830</v>
       </c>
     </row>
@@ -1789,48 +1867,48 @@
         <f aca="false">(B13-2)*COMBIN(B13-1, 1)</f>
         <v>90</v>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>195</v>
       </c>
       <c r="F13" s="1" t="n">
         <f aca="false">(G13-3)*COMBIN(G13-1, 2)</f>
         <v>360</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="17" t="n">
         <v>360</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <v>1710</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="17" t="n">
         <v>1845</v>
       </c>
       <c r="L13" s="1" t="n">
         <f aca="false">(M13-4)*COMBIN(M13-1, 3)</f>
         <v>840</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M13" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="N13" s="18" t="n">
+      <c r="N13" s="19" t="n">
         <v>840</v>
       </c>
-      <c r="O13" s="19" t="n">
+      <c r="O13" s="20" t="n">
         <v>6660</v>
       </c>
-      <c r="P13" s="11" t="n">
+      <c r="P13" s="12" t="n">
         <v>15690</v>
       </c>
-      <c r="Q13" s="18" t="n">
+      <c r="Q13" s="19" t="n">
         <v>11285</v>
       </c>
     </row>
@@ -1839,48 +1917,48 @@
         <f aca="false">(B14-2)*COMBIN(B14-1, 1)</f>
         <v>110</v>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="15" t="n">
         <v>110</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>209</v>
       </c>
       <c r="F14" s="1" t="n">
         <f aca="false">(G14-3)*COMBIN(G14-1, 2)</f>
         <v>495</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="17" t="n">
         <v>495</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="10" t="n">
         <v>2035</v>
       </c>
-      <c r="J14" s="16" t="n">
+      <c r="J14" s="17" t="n">
         <v>1936</v>
       </c>
       <c r="L14" s="1" t="n">
         <f aca="false">(M14-4)*COMBIN(M14-1, 3)</f>
         <v>1320</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="18" t="n">
+      <c r="N14" s="19" t="n">
         <v>1320</v>
       </c>
-      <c r="O14" s="19" t="n">
+      <c r="O14" s="20" t="n">
         <v>8910</v>
       </c>
-      <c r="P14" s="11" t="n">
+      <c r="P14" s="12" t="n">
         <v>18260</v>
       </c>
-      <c r="Q14" s="18" t="n">
+      <c r="Q14" s="19" t="n">
         <v>11649</v>
       </c>
     </row>
@@ -1889,48 +1967,48 @@
         <f aca="false">(B15-2)*COMBIN(B15-1, 1)</f>
         <v>132</v>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="15" t="n">
         <v>132</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>222</v>
       </c>
       <c r="F15" s="1" t="n">
         <f aca="false">(G15-3)*COMBIN(G15-1, 2)</f>
         <v>660</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="17" t="n">
         <v>660</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="10" t="n">
         <v>2376</v>
       </c>
-      <c r="J15" s="16" t="n">
+      <c r="J15" s="17" t="n">
         <v>2014</v>
       </c>
       <c r="L15" s="1" t="n">
         <f aca="false">(M15-4)*COMBIN(M15-1, 3)</f>
         <v>1980</v>
       </c>
-      <c r="M15" s="17" t="n">
+      <c r="M15" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="N15" s="18" t="n">
+      <c r="N15" s="19" t="n">
         <v>1980</v>
       </c>
-      <c r="O15" s="19" t="n">
+      <c r="O15" s="20" t="n">
         <v>11550</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="12" t="n">
         <v>20856</v>
       </c>
-      <c r="Q15" s="18" t="n">
+      <c r="Q15" s="19" t="n">
         <v>11935</v>
       </c>
     </row>
@@ -1939,48 +2017,48 @@
         <f aca="false">(B16-2)*COMBIN(B16-1, 1)</f>
         <v>156</v>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="15" t="n">
         <v>156</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>234</v>
       </c>
       <c r="F16" s="1" t="n">
         <f aca="false">(G16-3)*COMBIN(G16-1, 2)</f>
         <v>858</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" s="17" t="n">
         <v>858</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="10" t="n">
         <v>2730</v>
       </c>
-      <c r="J16" s="16" t="n">
+      <c r="J16" s="17" t="n">
         <v>2080</v>
       </c>
       <c r="L16" s="1" t="n">
         <f aca="false">(M16-4)*COMBIN(M16-1, 3)</f>
         <v>2860</v>
       </c>
-      <c r="M16" s="17" t="n">
+      <c r="M16" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="N16" s="18" t="n">
+      <c r="N16" s="19" t="n">
         <v>2860</v>
       </c>
-      <c r="O16" s="19" t="n">
+      <c r="O16" s="20" t="n">
         <v>14586</v>
       </c>
-      <c r="P16" s="11" t="n">
+      <c r="P16" s="12" t="n">
         <v>23452</v>
       </c>
-      <c r="Q16" s="18" t="n">
+      <c r="Q16" s="19" t="n">
         <v>12155</v>
       </c>
     </row>
@@ -1989,48 +2067,48 @@
         <f aca="false">(B17-2)*COMBIN(B17-1, 1)</f>
         <v>182</v>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="15" t="n">
         <v>182</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="15" t="n">
         <v>245</v>
       </c>
       <c r="F17" s="1" t="n">
         <f aca="false">(G17-3)*COMBIN(G17-1, 2)</f>
         <v>1092</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="17" t="n">
         <v>1092</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="10" t="n">
         <v>3094</v>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="17" t="n">
         <v>2135</v>
       </c>
       <c r="L17" s="1" t="n">
         <f aca="false">(M17-4)*COMBIN(M17-1, 3)</f>
         <v>4004</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="N17" s="18" t="n">
+      <c r="N17" s="19" t="n">
         <v>4004</v>
       </c>
-      <c r="O17" s="19" t="n">
+      <c r="O17" s="20" t="n">
         <v>18018</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" s="12" t="n">
         <v>26026</v>
       </c>
-      <c r="Q17" s="18" t="n">
+      <c r="Q17" s="19" t="n">
         <v>12320</v>
       </c>
     </row>
@@ -2039,48 +2117,48 @@
         <f aca="false">(B18-2)*COMBIN(B18-1, 1)</f>
         <v>210</v>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="15" t="n">
         <v>210</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <v>255</v>
       </c>
       <c r="F18" s="1" t="n">
         <f aca="false">(G18-3)*COMBIN(G18-1, 2)</f>
         <v>1365</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="H18" s="16" t="n">
+      <c r="H18" s="17" t="n">
         <v>1365</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="10" t="n">
         <v>3465</v>
       </c>
-      <c r="J18" s="16" t="n">
+      <c r="J18" s="17" t="n">
         <v>2180</v>
       </c>
       <c r="L18" s="1" t="n">
         <f aca="false">(M18-4)*COMBIN(M18-1, 3)</f>
         <v>5460</v>
       </c>
-      <c r="M18" s="17" t="n">
+      <c r="M18" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="N18" s="18" t="n">
+      <c r="N18" s="19" t="n">
         <v>5460</v>
       </c>
-      <c r="O18" s="19" t="n">
+      <c r="O18" s="20" t="n">
         <v>21840</v>
       </c>
-      <c r="P18" s="11" t="n">
+      <c r="P18" s="12" t="n">
         <v>28560</v>
       </c>
-      <c r="Q18" s="18" t="n">
+      <c r="Q18" s="19" t="n">
         <v>12440</v>
       </c>
     </row>
@@ -2089,48 +2167,48 @@
         <f aca="false">(B19-2)*COMBIN(B19-1, 1)</f>
         <v>240</v>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="15" t="n">
         <v>240</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="15" t="n">
         <v>264</v>
       </c>
       <c r="F19" s="1" t="n">
         <f aca="false">(G19-3)*COMBIN(G19-1, 2)</f>
         <v>1680</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H19" s="17" t="n">
         <v>1680</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="10" t="n">
         <v>3840</v>
       </c>
-      <c r="J19" s="16" t="n">
+      <c r="J19" s="17" t="n">
         <v>2216</v>
       </c>
       <c r="L19" s="1" t="n">
         <f aca="false">(M19-4)*COMBIN(M19-1, 3)</f>
         <v>7280</v>
       </c>
-      <c r="M19" s="17" t="n">
+      <c r="M19" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="N19" s="18" t="n">
+      <c r="N19" s="19" t="n">
         <v>7280</v>
       </c>
-      <c r="O19" s="19" t="n">
+      <c r="O19" s="20" t="n">
         <v>26040</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="12" t="n">
         <v>31040</v>
       </c>
-      <c r="Q19" s="18" t="n">
+      <c r="Q19" s="19" t="n">
         <v>12524</v>
       </c>
     </row>
@@ -2139,48 +2217,48 @@
         <f aca="false">(B20-2)*COMBIN(B20-1, 1)</f>
         <v>272</v>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="15" t="n">
         <v>272</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="15" t="n">
         <v>272</v>
       </c>
       <c r="F20" s="1" t="n">
         <f aca="false">(G20-3)*COMBIN(G20-1, 2)</f>
         <v>2040</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="17" t="n">
         <v>2040</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="10" t="n">
         <v>4216</v>
       </c>
-      <c r="J20" s="16" t="n">
+      <c r="J20" s="17" t="n">
         <v>2244</v>
       </c>
       <c r="L20" s="1" t="n">
         <f aca="false">(M20-4)*COMBIN(M20-1, 3)</f>
         <v>9520</v>
       </c>
-      <c r="M20" s="17" t="n">
+      <c r="M20" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="N20" s="18" t="n">
+      <c r="N20" s="19" t="n">
         <v>9520</v>
       </c>
-      <c r="O20" s="19" t="n">
+      <c r="O20" s="20" t="n">
         <v>30600</v>
       </c>
-      <c r="P20" s="11" t="n">
+      <c r="P20" s="12" t="n">
         <v>33456</v>
       </c>
-      <c r="Q20" s="18" t="n">
+      <c r="Q20" s="19" t="n">
         <v>12580</v>
       </c>
     </row>
@@ -2189,48 +2267,48 @@
         <f aca="false">(B21-2)*COMBIN(B21-1, 1)</f>
         <v>306</v>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B21" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="15" t="n">
         <v>306</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="15" t="n">
         <v>279</v>
       </c>
       <c r="F21" s="1" t="n">
         <f aca="false">(G21-3)*COMBIN(G21-1, 2)</f>
         <v>2448</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="H21" s="16" t="n">
+      <c r="H21" s="17" t="n">
         <v>2448</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="10" t="n">
         <v>4590</v>
       </c>
-      <c r="J21" s="16" t="n">
+      <c r="J21" s="17" t="n">
         <v>2265</v>
       </c>
       <c r="L21" s="1" t="n">
         <f aca="false">(M21-4)*COMBIN(M21-1, 3)</f>
         <v>12240</v>
       </c>
-      <c r="M21" s="17" t="n">
+      <c r="M21" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="N21" s="18" t="n">
+      <c r="N21" s="19" t="n">
         <v>12240</v>
       </c>
-      <c r="O21" s="19" t="n">
+      <c r="O21" s="20" t="n">
         <v>35496</v>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" s="12" t="n">
         <v>35802</v>
       </c>
-      <c r="Q21" s="18" t="n">
+      <c r="Q21" s="19" t="n">
         <v>12615</v>
       </c>
     </row>
@@ -2239,48 +2317,48 @@
         <f aca="false">(B22-2)*COMBIN(B22-1, 1)</f>
         <v>342</v>
       </c>
-      <c r="B22" s="13" t="n">
+      <c r="B22" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="15" t="n">
         <v>342</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="15" t="n">
         <v>285</v>
       </c>
       <c r="F22" s="1" t="n">
         <f aca="false">(G22-3)*COMBIN(G22-1, 2)</f>
         <v>2907</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G22" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H22" s="17" t="n">
         <v>2907</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="10" t="n">
         <v>4959</v>
       </c>
-      <c r="J22" s="16" t="n">
+      <c r="J22" s="17" t="n">
         <v>2280</v>
       </c>
       <c r="L22" s="1" t="n">
         <f aca="false">(M22-4)*COMBIN(M22-1, 3)</f>
         <v>15504</v>
       </c>
-      <c r="M22" s="17" t="n">
+      <c r="M22" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="N22" s="18" t="n">
+      <c r="N22" s="19" t="n">
         <v>15504</v>
       </c>
-      <c r="O22" s="19" t="n">
+      <c r="O22" s="20" t="n">
         <v>40698</v>
       </c>
-      <c r="P22" s="11" t="n">
+      <c r="P22" s="12" t="n">
         <v>38076</v>
       </c>
-      <c r="Q22" s="18" t="n">
+      <c r="Q22" s="19" t="n">
         <v>12635</v>
       </c>
     </row>
@@ -2289,48 +2367,48 @@
         <f aca="false">(B23-2)*COMBIN(B23-1, 1)</f>
         <v>380</v>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="15" t="n">
         <v>380</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="15" t="n">
         <v>290</v>
       </c>
       <c r="F23" s="1" t="n">
         <f aca="false">(G23-3)*COMBIN(G23-1, 2)</f>
         <v>3420</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="H23" s="16" t="n">
+      <c r="H23" s="17" t="n">
         <v>3420</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="10" t="n">
         <v>5320</v>
       </c>
-      <c r="J23" s="16" t="n">
+      <c r="J23" s="17" t="n">
         <v>2290</v>
       </c>
       <c r="L23" s="1" t="n">
         <f aca="false">(M23-4)*COMBIN(M23-1, 3)</f>
         <v>19380</v>
       </c>
-      <c r="M23" s="17" t="n">
+      <c r="M23" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="N23" s="18" t="n">
+      <c r="N23" s="19" t="n">
         <v>19380</v>
       </c>
-      <c r="O23" s="19" t="n">
+      <c r="O23" s="20" t="n">
         <v>46170</v>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" s="12" t="n">
         <v>40280</v>
       </c>
-      <c r="Q23" s="18" t="n">
+      <c r="Q23" s="19" t="n">
         <v>12645</v>
       </c>
     </row>
@@ -2339,48 +2417,48 @@
         <f aca="false">(B24-2)*COMBIN(B24-1, 1)</f>
         <v>420</v>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="15" t="n">
         <v>420</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="15" t="n">
         <v>294</v>
       </c>
       <c r="F24" s="1" t="n">
         <f aca="false">(G24-3)*COMBIN(G24-1, 2)</f>
         <v>3990</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="H24" s="16" t="n">
+      <c r="H24" s="17" t="n">
         <v>3990</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="10" t="n">
         <v>5670</v>
       </c>
-      <c r="J24" s="16" t="n">
+      <c r="J24" s="17" t="n">
         <v>2296</v>
       </c>
       <c r="L24" s="1" t="n">
         <f aca="false">(M24-4)*COMBIN(M24-1, 3)</f>
         <v>23940</v>
       </c>
-      <c r="M24" s="17" t="n">
+      <c r="M24" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="N24" s="18" t="n">
+      <c r="N24" s="19" t="n">
         <v>23940</v>
       </c>
-      <c r="O24" s="19" t="n">
+      <c r="O24" s="20" t="n">
         <v>51870</v>
       </c>
-      <c r="P24" s="11" t="n">
+      <c r="P24" s="12" t="n">
         <v>42420</v>
       </c>
-      <c r="Q24" s="18" t="n">
+      <c r="Q24" s="19" t="n">
         <v>12649</v>
       </c>
     </row>
@@ -2389,48 +2467,48 @@
         <f aca="false">(B25-2)*COMBIN(B25-1, 1)</f>
         <v>462</v>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="15" t="n">
         <v>462</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="15" t="n">
         <v>297</v>
       </c>
       <c r="F25" s="1" t="n">
         <f aca="false">(G25-3)*COMBIN(G25-1, 2)</f>
         <v>4620</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="H25" s="16" t="n">
+      <c r="H25" s="17" t="n">
         <v>4620</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="10" t="n">
         <v>6006</v>
       </c>
-      <c r="J25" s="16" t="n">
+      <c r="J25" s="17" t="n">
         <v>2299</v>
       </c>
       <c r="L25" s="1" t="n">
         <f aca="false">(M25-4)*COMBIN(M25-1, 3)</f>
         <v>29260</v>
       </c>
-      <c r="M25" s="17" t="n">
+      <c r="M25" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="N25" s="18" t="n">
+      <c r="N25" s="19" t="n">
         <v>29260</v>
       </c>
-      <c r="O25" s="19" t="n">
+      <c r="O25" s="20" t="n">
         <v>57750</v>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P25" s="12" t="n">
         <v>44506</v>
       </c>
-      <c r="Q25" s="18" t="n">
+      <c r="Q25" s="19" t="n">
         <v>12650</v>
       </c>
     </row>
@@ -2439,48 +2517,48 @@
         <f aca="false">(B26-2)*COMBIN(B26-1, 1)</f>
         <v>506</v>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="15" t="n">
         <v>506</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="15" t="n">
         <v>299</v>
       </c>
       <c r="F26" s="1" t="n">
         <f aca="false">(G26-3)*COMBIN(G26-1, 2)</f>
         <v>5313</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="H26" s="16" t="n">
+      <c r="H26" s="17" t="n">
         <v>5313</v>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="I26" s="10" t="n">
         <v>6325</v>
       </c>
-      <c r="J26" s="16" t="n">
+      <c r="J26" s="17" t="n">
         <v>2300</v>
       </c>
       <c r="L26" s="1" t="n">
         <f aca="false">(M26-4)*COMBIN(M26-1, 3)</f>
         <v>35420</v>
       </c>
-      <c r="M26" s="17" t="n">
+      <c r="M26" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="N26" s="18" t="n">
+      <c r="N26" s="19" t="n">
         <v>35420</v>
       </c>
-      <c r="O26" s="19" t="n">
+      <c r="O26" s="20" t="n">
         <v>63756</v>
       </c>
-      <c r="P26" s="11" t="n">
+      <c r="P26" s="12" t="n">
         <v>46552</v>
       </c>
-      <c r="Q26" s="18" t="n">
+      <c r="Q26" s="19" t="n">
         <v>12650</v>
       </c>
     </row>
@@ -2489,48 +2567,48 @@
         <f aca="false">(B27-2)*COMBIN(B27-1, 1)</f>
         <v>552</v>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="15" t="n">
         <v>552</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="15" t="n">
         <v>300</v>
       </c>
       <c r="F27" s="1" t="n">
         <f aca="false">(G27-3)*COMBIN(G27-1, 2)</f>
         <v>6072</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="H27" s="16" t="n">
+      <c r="H27" s="17" t="n">
         <v>6072</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="10" t="n">
         <v>6624</v>
       </c>
-      <c r="J27" s="16" t="n">
+      <c r="J27" s="17" t="n">
         <v>2300</v>
       </c>
       <c r="L27" s="1" t="n">
         <f aca="false">(M27-4)*COMBIN(M27-1, 3)</f>
         <v>42504</v>
       </c>
-      <c r="M27" s="17" t="n">
+      <c r="M27" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="N27" s="18" t="n">
+      <c r="N27" s="19" t="n">
         <v>42504</v>
       </c>
-      <c r="O27" s="19" t="n">
+      <c r="O27" s="20" t="n">
         <v>69828</v>
       </c>
-      <c r="P27" s="11" t="n">
+      <c r="P27" s="12" t="n">
         <v>48576</v>
       </c>
-      <c r="Q27" s="18" t="n">
+      <c r="Q27" s="19" t="n">
         <v>12650</v>
       </c>
     </row>
@@ -2539,531 +2617,531 @@
         <f aca="false">(B28-2)*COMBIN(B28-1, 1)</f>
         <v>600</v>
       </c>
-      <c r="B28" s="13" t="n">
+      <c r="B28" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>300</v>
       </c>
       <c r="F28" s="1" t="n">
         <f aca="false">(G28-3)*COMBIN(G28-1, 2)</f>
         <v>6900</v>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="G28" s="16" t="n">
         <v>26</v>
       </c>
-      <c r="H28" s="16" t="n">
+      <c r="H28" s="17" t="n">
         <v>6900</v>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I28" s="10" t="n">
         <v>6900</v>
       </c>
-      <c r="J28" s="16" t="n">
+      <c r="J28" s="17" t="n">
         <v>2300</v>
       </c>
       <c r="L28" s="1" t="n">
         <f aca="false">(M28-4)*COMBIN(M28-1, 3)</f>
         <v>50600</v>
       </c>
-      <c r="M28" s="17" t="n">
+      <c r="M28" s="18" t="n">
         <v>26</v>
       </c>
-      <c r="N28" s="18" t="n">
+      <c r="N28" s="19" t="n">
         <v>50600</v>
       </c>
-      <c r="O28" s="19" t="n">
+      <c r="O28" s="20" t="n">
         <v>75900</v>
       </c>
-      <c r="P28" s="11" t="n">
+      <c r="P28" s="12" t="n">
         <v>50600</v>
       </c>
-      <c r="Q28" s="18" t="n">
+      <c r="Q28" s="19" t="n">
         <v>12650</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13"/>
-      <c r="C29" s="14" t="n">
+      <c r="B29" s="14"/>
+      <c r="C29" s="15" t="n">
         <v>5200</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="15" t="n">
         <v>5200</v>
       </c>
-      <c r="E29" s="22" t="n">
+      <c r="E29" s="23" t="n">
         <v>10400</v>
       </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="16" t="n">
+      <c r="G29" s="16"/>
+      <c r="H29" s="17" t="n">
         <v>44850</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" s="10" t="n">
         <v>74750</v>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="17" t="n">
         <v>44850</v>
       </c>
-      <c r="K29" s="22" t="n">
+      <c r="K29" s="23" t="n">
         <v>164450</v>
       </c>
-      <c r="M29" s="17"/>
-      <c r="N29" s="18" t="n">
+      <c r="M29" s="18"/>
+      <c r="N29" s="19" t="n">
         <f aca="false">SUM(N3:N28)</f>
         <v>263120</v>
       </c>
-      <c r="O29" s="19" t="n">
+      <c r="O29" s="20" t="n">
         <f aca="false">SUM(O3:O28)</f>
         <v>592020</v>
       </c>
-      <c r="P29" s="11" t="n">
+      <c r="P29" s="12" t="n">
         <f aca="false">SUM(P3:P28)</f>
         <v>592020</v>
       </c>
-      <c r="Q29" s="18" t="n">
+      <c r="Q29" s="19" t="n">
         <f aca="false">SUM(Q3:Q28)</f>
         <v>263120</v>
       </c>
-      <c r="R29" s="22" t="n">
+      <c r="R29" s="23" t="n">
         <f aca="false">SUM(N29:Q29)</f>
         <v>1710280</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="2" t="n">
         <f aca="false">COMBIN(26,$F$1)*COMBIN($F$1-1,H2-1)</f>
         <v>44850</v>
       </c>
-      <c r="I30" s="0" t="n">
+      <c r="I30" s="2" t="n">
         <f aca="false">COMBIN(26,$F$1)*COMBIN($F$1-1,I2-1)</f>
         <v>44850</v>
       </c>
-      <c r="J30" s="0" t="n">
+      <c r="J30" s="2" t="n">
         <f aca="false">COMBIN(26,$F$1)*COMBIN($F$1-1,J2-1)</f>
         <v>14950</v>
       </c>
-      <c r="K30" s="0" t="n">
+      <c r="K30" s="2" t="n">
         <f aca="false">K29/2</f>
         <v>82225</v>
       </c>
-      <c r="N30" s="0" t="n">
+      <c r="N30" s="2" t="n">
         <f aca="false">COMBIN(26,$L$1)*COMBIN($L$1-1,N2-1)</f>
         <v>263120</v>
       </c>
-      <c r="O30" s="0" t="n">
+      <c r="O30" s="2" t="n">
         <f aca="false">COMBIN(26,$L$1)*COMBIN($L$1-1,O2-1)</f>
         <v>394680</v>
       </c>
-      <c r="P30" s="0" t="n">
+      <c r="P30" s="2" t="n">
         <f aca="false">COMBIN(26,$L$1)*COMBIN($L$1-1,P2-1)</f>
         <v>263120</v>
       </c>
-      <c r="Q30" s="0" t="n">
+      <c r="Q30" s="2" t="n">
         <f aca="false">COMBIN(26,$L$1)*COMBIN($L$1-1,Q2-1)</f>
         <v>65780</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J31" s="0" t="n">
+      <c r="J31" s="2" t="n">
         <f aca="false">I29/J30</f>
         <v>5</v>
       </c>
-      <c r="L31" s="23" t="s">
+      <c r="L31" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="M31" s="23" t="s">
+      <c r="M31" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="N31" s="23" t="s">
+      <c r="N31" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="2" t="n">
         <v>29645</v>
       </c>
-      <c r="J32" s="0" t="n">
+      <c r="J32" s="2" t="n">
         <f aca="false">K32*O32</f>
         <v>0</v>
       </c>
-      <c r="K32" s="0" t="n">
+      <c r="K32" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L32" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="M32" s="0" t="n">
+      <c r="L32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N32" s="0" t="n">
+      <c r="N32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="0" t="n">
+      <c r="O32" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="2" t="n">
         <v>67045</v>
       </c>
-      <c r="J33" s="0" t="n">
+      <c r="J33" s="2" t="n">
         <f aca="false">K33*O33</f>
         <v>44</v>
       </c>
-      <c r="K33" s="0" t="n">
+      <c r="K33" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L33" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M33" s="0" t="n">
+      <c r="L33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N33" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" s="0" t="n">
+      <c r="N33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="2" t="n">
         <v>61985</v>
       </c>
-      <c r="J34" s="0" t="n">
+      <c r="J34" s="2" t="n">
         <f aca="false">K34*O34</f>
         <v>0</v>
       </c>
-      <c r="K34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="0" t="n">
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="0" t="n">
+      <c r="M34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" s="0" t="n">
+      <c r="N34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="2" t="n">
         <v>33649</v>
       </c>
-      <c r="J35" s="0" t="n">
+      <c r="J35" s="2" t="n">
         <f aca="false">K35*O35</f>
         <v>22</v>
       </c>
-      <c r="K35" s="0" t="n">
+      <c r="K35" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L35" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" s="0" t="n">
+      <c r="L35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="O35" s="0" t="n">
+      <c r="N35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L40" s="23" t="s">
+      <c r="L40" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="M40" s="23" t="s">
+      <c r="M40" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="N40" s="23" t="s">
+      <c r="N40" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J41" s="0" t="n">
+      <c r="J41" s="2" t="n">
         <f aca="false">K41*O41</f>
         <v>0</v>
       </c>
-      <c r="K41" s="0" t="n">
+      <c r="K41" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="L41" s="0" t="n">
+      <c r="L41" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M41" s="0" t="n">
+      <c r="M41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N41" s="0" t="n">
+      <c r="N41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O41" s="0" t="n">
+      <c r="O41" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J42" s="24" t="n">
+      <c r="J42" s="25" t="n">
         <f aca="false">K42*O42</f>
         <v>22</v>
       </c>
-      <c r="K42" s="24" t="n">
+      <c r="K42" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="L42" s="24" t="n">
+      <c r="L42" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="M42" s="24" t="n">
+      <c r="M42" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="N42" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O42" s="24" t="n">
+      <c r="N42" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J43" s="24" t="n">
+      <c r="J43" s="25" t="n">
         <f aca="false">K43*O43</f>
         <v>44</v>
       </c>
-      <c r="K43" s="24" t="n">
+      <c r="K43" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="L43" s="24" t="n">
+      <c r="L43" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="M43" s="24" t="n">
+      <c r="M43" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="N43" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O43" s="24" t="n">
+      <c r="N43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" s="25" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J44" s="24" t="n">
+      <c r="J44" s="25" t="n">
         <f aca="false">K44*O44</f>
         <v>63</v>
       </c>
-      <c r="K44" s="24" t="n">
+      <c r="K44" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="L44" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M44" s="24" t="n">
+      <c r="L44" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="N44" s="24" t="n">
+      <c r="N44" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="O44" s="24" t="n">
+      <c r="O44" s="25" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J45" s="24" t="n">
+      <c r="J45" s="25" t="n">
         <f aca="false">K45*O45</f>
         <v>22</v>
       </c>
-      <c r="K45" s="24" t="n">
+      <c r="K45" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="L45" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" s="24" t="n">
+      <c r="L45" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="N45" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O45" s="24" t="n">
+      <c r="N45" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J46" s="0" t="n">
+      <c r="J46" s="2" t="n">
         <f aca="false">K46*O46</f>
         <v>0</v>
       </c>
-      <c r="K46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" s="0" t="n">
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N46" s="0" t="n">
+      <c r="N46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O46" s="0" t="n">
+      <c r="O46" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J47" s="24" t="n">
+      <c r="J47" s="25" t="n">
         <f aca="false">K47*O47</f>
         <v>63</v>
       </c>
-      <c r="K47" s="24" t="n">
+      <c r="K47" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="L47" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" s="24" t="n">
+      <c r="L47" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="N47" s="24" t="n">
+      <c r="N47" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="O47" s="24" t="n">
+      <c r="O47" s="25" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J48" s="24" t="n">
+      <c r="J48" s="25" t="n">
         <f aca="false">K48*O48</f>
         <v>44</v>
       </c>
-      <c r="K48" s="24" t="n">
+      <c r="K48" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="L48" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M48" s="24" t="n">
+      <c r="L48" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="N48" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O48" s="24" t="n">
+      <c r="N48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" s="25" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J49" s="0" t="n">
+      <c r="J49" s="2" t="n">
         <f aca="false">K49*O49</f>
         <v>0</v>
       </c>
-      <c r="K49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="M49" s="0" t="n">
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N49" s="0" t="n">
+      <c r="N49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O49" s="0" t="n">
+      <c r="O49" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J50" s="0" t="n">
+      <c r="J50" s="2" t="n">
         <f aca="false">K50*O50</f>
         <v>0</v>
       </c>
-      <c r="K50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="0" t="n">
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M50" s="0" t="n">
+      <c r="M50" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N50" s="0" t="n">
+      <c r="N50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O50" s="0" t="n">
+      <c r="O50" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J51" s="0" t="n">
+      <c r="J51" s="2" t="n">
         <f aca="false">K51*O51</f>
         <v>0</v>
       </c>
-      <c r="K51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="0" t="n">
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M51" s="0" t="n">
+      <c r="M51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="O51" s="0" t="n">
+      <c r="N51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J52" s="0" t="n">
+      <c r="J52" s="2" t="n">
         <f aca="false">K52*O52</f>
         <v>0</v>
       </c>
-      <c r="K52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="0" t="n">
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M52" s="0" t="n">
+      <c r="M52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N52" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="O52" s="0" t="n">
+      <c r="N52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J53" s="0" t="n">
+      <c r="J53" s="2" t="n">
         <f aca="false">SUM(J41:J52)</f>
         <v>258</v>
       </c>
@@ -3085,7 +3163,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -3098,226 +3176,226 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="25"/>
-      <c r="C3" s="26" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+    </row>
+    <row r="3" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="26"/>
+      <c r="C3" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="30" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="25"/>
-      <c r="C4" s="30" t="n">
+      <c r="B4" s="26"/>
+      <c r="C4" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="32" t="n">
+      <c r="E4" s="33" t="n">
         <v>0.523</v>
       </c>
-      <c r="F4" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00021</v>
-      </c>
-      <c r="H4" s="30" t="s">
+      <c r="F4" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="31" t="n">
+        <f aca="false">0.00015+RANDBETWEEN(-10,10)/100000</f>
+        <v>0.00024</v>
+      </c>
+      <c r="H4" s="31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25"/>
-      <c r="C5" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.51</v>
-      </c>
-      <c r="F5" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>5E-005</v>
-      </c>
-      <c r="H5" s="30" t="s">
+      <c r="E5" s="33" t="n">
+        <f aca="false">E$4+RANDBETWEEN(-100,100)/1000</f>
+        <v>0.553</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <f aca="false">0.00015+RANDBETWEEN(-10,10)/100000</f>
+        <v>0.00022</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25"/>
-      <c r="C6" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="31" t="s">
+      <c r="B6" s="26"/>
+      <c r="C6" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.553</v>
-      </c>
-      <c r="F6" s="33" t="n">
+      <c r="E6" s="33" t="n">
+        <f aca="false">E$4+RANDBETWEEN(-100,100)/1000</f>
+        <v>0.568</v>
+      </c>
+      <c r="F6" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00023</v>
-      </c>
-      <c r="H6" s="30" t="s">
+      <c r="G6" s="31" t="n">
+        <f aca="false">0.00015+RANDBETWEEN(-10,10)/100000</f>
+        <v>0.00019</v>
+      </c>
+      <c r="H6" s="31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25"/>
-      <c r="C7" s="30" t="n">
+      <c r="B7" s="26"/>
+      <c r="C7" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="35" t="n">
         <f aca="false">E$4+0.7</f>
         <v>1.223</v>
       </c>
-      <c r="F7" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00015</v>
-      </c>
-      <c r="H7" s="30" t="s">
+      <c r="F7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <f aca="false">0.00015+RANDBETWEEN(-10,10)/100000</f>
+        <v>7E-005</v>
+      </c>
+      <c r="H7" s="31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25"/>
-      <c r="C8" s="30" t="n">
+      <c r="B8" s="26"/>
+      <c r="C8" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.423</v>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00023</v>
-      </c>
-      <c r="H8" s="33" t="n">
+      <c r="E8" s="33" t="n">
+        <f aca="false">E$4+RANDBETWEEN(-100,100)/1000</f>
+        <v>0.614</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <f aca="false">0.00015+RANDBETWEEN(-10,10)/100000</f>
+        <v>5E-005</v>
+      </c>
+      <c r="H8" s="34" t="n">
         <v>-2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25"/>
-      <c r="C9" s="30" t="n">
+      <c r="B9" s="26"/>
+      <c r="C9" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.49</v>
-      </c>
-      <c r="F9" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.00025</v>
-      </c>
-      <c r="H9" s="30" t="s">
+      <c r="E9" s="33" t="n">
+        <f aca="false">E$4+RANDBETWEEN(-100,100)/1000</f>
+        <v>0.451</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="31" t="n">
+        <f aca="false">0.00015+RANDBETWEEN(-10,10)/100000</f>
+        <v>0.00011</v>
+      </c>
+      <c r="H9" s="31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="25"/>
-      <c r="C10" s="30" t="n">
+      <c r="B10" s="26"/>
+      <c r="C10" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.544</v>
-      </c>
-      <c r="F10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+      <c r="E10" s="33" t="n">
+        <f aca="false">E$4+RANDBETWEEN(-100,100)/1000</f>
+        <v>0.553</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <f aca="false">0.00015+RANDBETWEEN(-10,10)/100000</f>
+        <v>6E-005</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="26"/>
+      <c r="C11" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <f aca="false">E$4+RANDBETWEEN(-100,100)/1000</f>
+        <v>0.487</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="31" t="n">
+        <f aca="false">0.00015+RANDBETWEEN(-10,10)/100000</f>
         <v>9E-005</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H11" s="31" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="25"/>
-      <c r="C11" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
-        <v>0.603</v>
-      </c>
-      <c r="F11" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
-        <v>0.0002</v>
-      </c>
-      <c r="H11" s="30" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3331,1285 +3409,1285 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q58"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="11.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="11" style="0" width="9.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="6.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="11.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="11" style="2" width="9.81"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" s="11" t="n">
+      <c r="B2" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F2" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="11" t="n">
+      <c r="G2" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" s="0" t="n">
+      <c r="K2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P2" s="0" t="n">
+      <c r="P2" s="2" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="0" t="n">
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="0" t="n">
+      <c r="K3" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <f aca="false">L33</f>
         <v>0</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="2" t="n">
         <f aca="false">M33</f>
         <v>0</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="2" t="n">
         <f aca="false">N33</f>
         <v>0</v>
       </c>
-      <c r="O3" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="35" t="n">
+      <c r="O3" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="0" t="n">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>42504</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="0" t="n">
+      <c r="J4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
         <f aca="false">L34</f>
         <v>0</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="2" t="n">
         <f aca="false">M34</f>
         <v>0</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="2" t="n">
         <f aca="false">N34</f>
         <v>0</v>
       </c>
-      <c r="O4" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="35" t="n">
+      <c r="O4" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="36" t="n">
         <v>42504</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="n">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>17710</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="2" t="n">
         <v>76153</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="0" t="n">
+      <c r="J5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n">
         <f aca="false">L35</f>
         <v>0</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="2" t="n">
         <f aca="false">M35</f>
         <v>0</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="2" t="n">
         <f aca="false">N35</f>
         <v>0</v>
       </c>
-      <c r="O5" s="35" t="n">
+      <c r="O5" s="36" t="n">
         <v>17710</v>
       </c>
-      <c r="P5" s="35" t="n">
+      <c r="P5" s="36" t="n">
         <v>76153</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="21" t="n">
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="22" t="n">
         <v>4620</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="2" t="n">
         <v>48510</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="2" t="n">
         <v>102487</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0" t="n">
+      <c r="K6" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="n">
         <f aca="false">L36</f>
         <v>0</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="2" t="n">
         <f aca="false">M36</f>
         <v>0</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="2" t="n">
         <f aca="false">N36</f>
         <v>4620</v>
       </c>
-      <c r="O6" s="35" t="n">
+      <c r="O6" s="36" t="n">
         <v>48510</v>
       </c>
-      <c r="P6" s="35" t="n">
+      <c r="P6" s="36" t="n">
         <v>102487</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="21" t="n">
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="22" t="n">
         <v>840</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="22" t="n">
         <v>17220</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="2" t="n">
         <v>88620</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="2" t="n">
         <v>122836</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="0" t="n">
+      <c r="K7" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="n">
         <f aca="false">L37</f>
         <v>0</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="2" t="n">
         <f aca="false">M37</f>
         <v>0</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="2" t="n">
         <f aca="false">N37</f>
         <v>15960</v>
       </c>
-      <c r="O7" s="35" t="n">
+      <c r="O7" s="36" t="n">
         <v>88620</v>
       </c>
-      <c r="P7" s="35" t="n">
+      <c r="P7" s="36" t="n">
         <v>122836</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="21" t="n">
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="22" t="n">
         <v>4000</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="22" t="n">
         <v>40100</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="2" t="n">
         <v>135000</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="2" t="n">
         <v>138340</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="0" t="n">
+      <c r="K8" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <f aca="false">L38</f>
         <v>0</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="2" t="n">
         <f aca="false">M38</f>
         <v>950</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="2" t="n">
         <f aca="false">N38</f>
         <v>34200</v>
       </c>
-      <c r="O8" s="35" t="n">
+      <c r="O8" s="36" t="n">
         <v>135000</v>
       </c>
-      <c r="P8" s="35" t="n">
+      <c r="P8" s="36" t="n">
         <v>138340</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="22" t="n">
         <v>585</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="22" t="n">
         <v>11420</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="22" t="n">
         <v>74685</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="2" t="n">
         <v>185256</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="2" t="n">
         <v>149968</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K9" s="35" t="n">
+      <c r="K9" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="2" t="n">
         <f aca="false">L39</f>
         <v>0</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="2" t="n">
         <f aca="false">M39</f>
         <v>4104</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="2" t="n">
         <f aca="false">N39</f>
         <v>58140</v>
       </c>
-      <c r="O9" s="35" t="n">
+      <c r="O9" s="36" t="n">
         <v>185256</v>
       </c>
-      <c r="P9" s="35" t="n">
+      <c r="P9" s="36" t="n">
         <v>149968</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="22" t="n">
         <v>1995</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="22" t="n">
         <v>25340</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="22" t="n">
         <v>121695</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="2" t="n">
         <v>237552</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="2" t="n">
         <v>158536</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K10" s="35" t="n">
+      <c r="K10" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="2" t="n">
         <f aca="false">L40</f>
         <v>126</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="2" t="n">
         <f aca="false">M40</f>
         <v>10710</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="2" t="n">
         <f aca="false">N40</f>
         <v>85680</v>
       </c>
-      <c r="O10" s="35" t="n">
+      <c r="O10" s="36" t="n">
         <v>237552</v>
       </c>
-      <c r="P10" s="35" t="n">
+      <c r="P10" s="36" t="n">
         <v>158536</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="22" t="n">
         <v>5180</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>48160</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="22" t="n">
         <v>181300</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="2" t="n">
         <v>290528</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="2" t="n">
         <v>164724</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K11" s="35" t="n">
+      <c r="K11" s="36" t="n">
         <v>168</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="2" t="n">
         <f aca="false">L41</f>
         <v>680</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="2" t="n">
         <f aca="false">M41</f>
         <v>21760</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="2" t="n">
         <f aca="false">N41</f>
         <v>114240</v>
       </c>
-      <c r="O11" s="35" t="n">
+      <c r="O11" s="36" t="n">
         <v>290528</v>
       </c>
-      <c r="P11" s="35" t="n">
+      <c r="P11" s="36" t="n">
         <v>164724</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="2" t="n">
         <v>504</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="22" t="n">
         <v>11340</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>82320</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="22" t="n">
         <v>253260</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="2" t="n">
         <v>343224</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="2" t="n">
         <v>169092</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="35" t="n">
+      <c r="K12" s="36" t="n">
         <v>504</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="2" t="n">
         <f aca="false">L42</f>
         <v>2160</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="2" t="n">
         <f aca="false">M42</f>
         <v>37800</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="2" t="n">
         <f aca="false">N42</f>
         <v>141120</v>
       </c>
-      <c r="O12" s="35" t="n">
+      <c r="O12" s="36" t="n">
         <v>343224</v>
       </c>
-      <c r="P12" s="35" t="n">
+      <c r="P12" s="36" t="n">
         <v>169092</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="22" t="n">
         <v>22050</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>130200</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="22" t="n">
         <v>337050</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="2" t="n">
         <v>395010</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="2" t="n">
         <v>172095</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K13" s="35" t="n">
+      <c r="K13" s="36" t="n">
         <v>1260</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="2" t="n">
         <f aca="false">L43</f>
         <v>5250</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="2" t="n">
         <f aca="false">M43</f>
         <v>58800</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="2" t="n">
         <f aca="false">N43</f>
         <v>163800</v>
       </c>
-      <c r="O13" s="35" t="n">
+      <c r="O13" s="36" t="n">
         <v>395010</v>
       </c>
-      <c r="P13" s="35" t="n">
+      <c r="P13" s="36" t="n">
         <v>172095</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="2" t="n">
         <v>2772</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="22" t="n">
         <v>39270</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>194040</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="22" t="n">
         <v>431970</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="2" t="n">
         <v>445522</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="2" t="n">
         <v>174097</v>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K14" s="35" t="n">
+      <c r="K14" s="36" t="n">
         <v>2772</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="2" t="n">
         <f aca="false">L44</f>
         <v>10780</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="2" t="n">
         <f aca="false">M44</f>
         <v>84084</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="2" t="n">
         <f aca="false">N44</f>
         <v>180180</v>
       </c>
-      <c r="O14" s="35" t="n">
+      <c r="O14" s="36" t="n">
         <v>445522</v>
       </c>
-      <c r="P14" s="35" t="n">
+      <c r="P14" s="36" t="n">
         <v>174097</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="2" t="n">
         <v>5544</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="22" t="n">
         <v>65340</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="22" t="n">
         <v>275880</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="22" t="n">
         <v>537240</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="2" t="n">
         <v>494604</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="2" t="n">
         <v>175384</v>
       </c>
-      <c r="J15" s="0" t="n">
+      <c r="J15" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K15" s="35" t="n">
+      <c r="K15" s="36" t="n">
         <v>5544</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="2" t="n">
         <f aca="false">L45</f>
         <v>19656</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="2" t="n">
         <f aca="false">M45</f>
         <v>112320</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="2" t="n">
         <f aca="false">N45</f>
         <v>188760</v>
       </c>
-      <c r="O15" s="35" t="n">
+      <c r="O15" s="36" t="n">
         <v>494604</v>
       </c>
-      <c r="P15" s="35" t="n">
+      <c r="P15" s="36" t="n">
         <v>175384</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="2" t="n">
         <v>10296</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="22" t="n">
         <v>102960</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="22" t="n">
         <v>377520</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="22" t="n">
         <v>652080</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="2" t="n">
         <v>542256</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="2" t="n">
         <v>176176</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="J16" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="K16" s="35" t="n">
+      <c r="K16" s="36" t="n">
         <v>10296</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16" s="2" t="n">
         <f aca="false">L46</f>
         <v>32760</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="2" t="n">
         <f aca="false">M46</f>
         <v>141570</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="2" t="n">
         <f aca="false">N46</f>
         <v>188760</v>
       </c>
-      <c r="O16" s="35" t="n">
+      <c r="O16" s="36" t="n">
         <v>542256</v>
       </c>
-      <c r="P16" s="35" t="n">
+      <c r="P16" s="36" t="n">
         <v>176176</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="2" t="n">
         <v>18018</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="22" t="n">
         <v>155155</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="22" t="n">
         <v>500500</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="22" t="n">
         <v>775775</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="2" t="n">
         <v>588588</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="2" t="n">
         <v>176638</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K17" s="35" t="n">
+      <c r="K17" s="36" t="n">
         <v>18018</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="2" t="n">
         <f aca="false">L47</f>
         <v>50820</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="2" t="n">
         <f aca="false">M47</f>
         <v>169400</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="2" t="n">
         <f aca="false">N47</f>
         <v>180180</v>
       </c>
-      <c r="O17" s="35" t="n">
+      <c r="O17" s="36" t="n">
         <v>588588</v>
       </c>
-      <c r="P17" s="35" t="n">
+      <c r="P17" s="36" t="n">
         <v>176638</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="2" t="n">
         <v>30030</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="22" t="n">
         <v>225225</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="22" t="n">
         <v>646100</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="22" t="n">
         <v>907725</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="2" t="n">
         <v>633780</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="2" t="n">
         <v>176890</v>
       </c>
-      <c r="J18" s="0" t="n">
+      <c r="J18" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="K18" s="35" t="n">
+      <c r="K18" s="36" t="n">
         <v>30030</v>
       </c>
-      <c r="L18" s="0" t="n">
+      <c r="L18" s="2" t="n">
         <f aca="false">L48</f>
         <v>74250</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18" s="2" t="n">
         <f aca="false">M48</f>
         <v>193050</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="2" t="n">
         <f aca="false">N48</f>
         <v>163800</v>
       </c>
-      <c r="O18" s="35" t="n">
+      <c r="O18" s="36" t="n">
         <v>633780</v>
       </c>
-      <c r="P18" s="35" t="n">
+      <c r="P18" s="36" t="n">
         <v>176890</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="2" t="n">
         <v>48048</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="22" t="n">
         <v>316680</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="22" t="n">
         <v>815360</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="22" t="n">
         <v>1047480</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="2" t="n">
         <v>678048</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="2" t="n">
         <v>177016</v>
       </c>
-      <c r="J19" s="0" t="n">
+      <c r="J19" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K19" s="35" t="n">
+      <c r="K19" s="36" t="n">
         <v>48048</v>
       </c>
-      <c r="L19" s="0" t="n">
+      <c r="L19" s="2" t="n">
         <f aca="false">L49</f>
         <v>102960</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19" s="2" t="n">
         <f aca="false">M49</f>
         <v>209664</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="2" t="n">
         <f aca="false">N49</f>
         <v>141120</v>
       </c>
-      <c r="O19" s="35" t="n">
+      <c r="O19" s="36" t="n">
         <v>678048</v>
       </c>
-      <c r="P19" s="35" t="n">
+      <c r="P19" s="36" t="n">
         <v>177016</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="2" t="n">
         <v>74256</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="22" t="n">
         <v>433160</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="22" t="n">
         <v>1009120</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E20" s="22" t="n">
         <v>1194760</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="2" t="n">
         <v>721616</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="2" t="n">
         <v>177072</v>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J20" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K20" s="35" t="n">
+      <c r="K20" s="36" t="n">
         <v>74256</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="2" t="n">
         <f aca="false">L50</f>
         <v>136136</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="2" t="n">
         <f aca="false">M50</f>
         <v>216580</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="2" t="n">
         <f aca="false">N50</f>
         <v>114240</v>
       </c>
-      <c r="O20" s="35" t="n">
+      <c r="O20" s="36" t="n">
         <v>721616</v>
       </c>
-      <c r="P20" s="35" t="n">
+      <c r="P20" s="36" t="n">
         <v>177072</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="2" t="n">
         <v>111384</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="22" t="n">
         <v>578340</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="22" t="n">
         <v>1228080</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="22" t="n">
         <v>1349460</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="2" t="n">
         <v>764694</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="2" t="n">
         <v>177093</v>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="J21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="K21" s="35" t="n">
+      <c r="K21" s="36" t="n">
         <v>111384</v>
       </c>
-      <c r="L21" s="0" t="n">
+      <c r="L21" s="2" t="n">
         <f aca="false">L51</f>
         <v>171990</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="M21" s="2" t="n">
         <f aca="false">M51</f>
         <v>211680</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="2" t="n">
         <f aca="false">N51</f>
         <v>85680</v>
       </c>
-      <c r="O21" s="35" t="n">
+      <c r="O21" s="36" t="n">
         <v>764694</v>
       </c>
-      <c r="P21" s="35" t="n">
+      <c r="P21" s="36" t="n">
         <v>177093</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="2" t="n">
         <v>162792</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="22" t="n">
         <v>755820</v>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="22" t="n">
         <v>1472880</v>
       </c>
-      <c r="E22" s="21" t="n">
+      <c r="E22" s="22" t="n">
         <v>1511640</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="2" t="n">
         <v>807462</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="G22" s="2" t="n">
         <v>177099</v>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="J22" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K22" s="35" t="n">
+      <c r="K22" s="36" t="n">
         <v>162792</v>
       </c>
-      <c r="L22" s="0" t="n">
+      <c r="L22" s="2" t="n">
         <f aca="false">L52</f>
         <v>207480</v>
       </c>
-      <c r="M22" s="0" t="n">
+      <c r="M22" s="2" t="n">
         <f aca="false">M52</f>
         <v>193800</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22" s="2" t="n">
         <f aca="false">N52</f>
         <v>58140</v>
       </c>
-      <c r="O22" s="35" t="n">
+      <c r="O22" s="36" t="n">
         <v>807462</v>
       </c>
-      <c r="P22" s="35" t="n">
+      <c r="P22" s="36" t="n">
         <v>177099</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="2" t="n">
         <v>232560</v>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="22" t="n">
         <v>969000</v>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D23" s="22" t="n">
         <v>1744200</v>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E23" s="22" t="n">
         <v>1681500</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="2" t="n">
         <v>850060</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="G23" s="2" t="n">
         <v>177100</v>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J23" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="K23" s="35" t="n">
+      <c r="K23" s="36" t="n">
         <v>232560</v>
       </c>
-      <c r="L23" s="0" t="n">
+      <c r="L23" s="2" t="n">
         <f aca="false">L53</f>
         <v>238000</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="M23" s="2" t="n">
         <f aca="false">M53</f>
         <v>163200</v>
       </c>
-      <c r="N23" s="0" t="n">
+      <c r="N23" s="2" t="n">
         <f aca="false">N53</f>
         <v>34200</v>
       </c>
-      <c r="O23" s="35" t="n">
+      <c r="O23" s="36" t="n">
         <v>850060</v>
       </c>
-      <c r="P23" s="35" t="n">
+      <c r="P23" s="36" t="n">
         <v>177100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="2" t="n">
         <v>325584</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="22" t="n">
         <v>1220940</v>
       </c>
-      <c r="D24" s="21" t="n">
+      <c r="D24" s="22" t="n">
         <v>2042880</v>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E24" s="22" t="n">
         <v>1859340</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="2" t="n">
         <v>892584</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24" s="2" t="n">
         <v>177100</v>
       </c>
-      <c r="J24" s="0" t="n">
+      <c r="J24" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="K24" s="35" t="n">
+      <c r="K24" s="36" t="n">
         <v>325584</v>
       </c>
-      <c r="L24" s="0" t="n">
+      <c r="L24" s="2" t="n">
         <f aca="false">L54</f>
         <v>257040</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24" s="2" t="n">
         <f aca="false">M54</f>
         <v>122094</v>
       </c>
-      <c r="N24" s="0" t="n">
+      <c r="N24" s="2" t="n">
         <f aca="false">N54</f>
         <v>15960</v>
       </c>
-      <c r="O24" s="35" t="n">
+      <c r="O24" s="36" t="n">
         <v>892584</v>
       </c>
-      <c r="P24" s="35" t="n">
+      <c r="P24" s="36" t="n">
         <v>177100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="2" t="n">
         <v>447678</v>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="22" t="n">
         <v>1514205</v>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D25" s="22" t="n">
         <v>2370060</v>
       </c>
-      <c r="E25" s="21" t="n">
+      <c r="E25" s="22" t="n">
         <v>2045505</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="2" t="n">
         <v>935088</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25" s="2" t="n">
         <v>177100</v>
       </c>
-      <c r="J25" s="0" t="n">
+      <c r="J25" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="K25" s="35" t="n">
+      <c r="K25" s="36" t="n">
         <v>447678</v>
       </c>
-      <c r="L25" s="0" t="n">
+      <c r="L25" s="2" t="n">
         <f aca="false">L55</f>
         <v>255816</v>
       </c>
-      <c r="M25" s="0" t="n">
+      <c r="M25" s="2" t="n">
         <f aca="false">M55</f>
         <v>75240</v>
       </c>
-      <c r="N25" s="0" t="n">
+      <c r="N25" s="2" t="n">
         <f aca="false">N55</f>
         <v>4620</v>
       </c>
-      <c r="O25" s="35" t="n">
+      <c r="O25" s="36" t="n">
         <v>935088</v>
       </c>
-      <c r="P25" s="35" t="n">
+      <c r="P25" s="36" t="n">
         <v>177100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="2" t="n">
         <v>605682</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="22" t="n">
         <v>1850695</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="22" t="n">
         <v>2727340</v>
       </c>
-      <c r="E26" s="21" t="n">
+      <c r="E26" s="22" t="n">
         <v>2240315</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="2" t="n">
         <v>977592</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="2" t="n">
         <v>177100</v>
       </c>
-      <c r="J26" s="0" t="n">
+      <c r="J26" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K26" s="35" t="n">
+      <c r="K26" s="36" t="n">
         <v>605682</v>
       </c>
-      <c r="L26" s="0" t="n">
+      <c r="L26" s="2" t="n">
         <f aca="false">L56</f>
         <v>222870</v>
       </c>
-      <c r="M26" s="0" t="n">
+      <c r="M26" s="2" t="n">
         <f aca="false">M56</f>
         <v>30590</v>
       </c>
-      <c r="N26" s="0" t="n">
+      <c r="N26" s="2" t="n">
         <f aca="false">N56</f>
         <v>0</v>
       </c>
-      <c r="O26" s="35" t="n">
+      <c r="O26" s="36" t="n">
         <v>977592</v>
       </c>
-      <c r="P26" s="35" t="n">
+      <c r="P26" s="36" t="n">
         <v>177100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="2" t="n">
         <v>807576</v>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="22" t="n">
         <v>2231460</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="22" t="n">
         <v>3116960</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="22" t="n">
         <v>2443980</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="2" t="n">
         <v>1020096</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27" s="2" t="n">
         <v>177100</v>
       </c>
-      <c r="J27" s="0" t="n">
+      <c r="J27" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="K27" s="35" t="n">
+      <c r="K27" s="36" t="n">
         <v>807576</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27" s="2" t="n">
         <f aca="false">L57</f>
         <v>143640</v>
       </c>
-      <c r="M27" s="0" t="n">
+      <c r="M27" s="2" t="n">
         <f aca="false">M57</f>
         <v>0</v>
       </c>
-      <c r="N27" s="0" t="n">
+      <c r="N27" s="2" t="n">
         <f aca="false">N57</f>
         <v>0</v>
       </c>
-      <c r="O27" s="35" t="n">
+      <c r="O27" s="36" t="n">
         <v>1020096</v>
       </c>
-      <c r="P27" s="35" t="n">
+      <c r="P27" s="36" t="n">
         <v>177100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="2" t="n">
         <v>1062600</v>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="22" t="n">
         <v>2656500</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="22" t="n">
         <v>3542000</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="22" t="n">
         <v>2656500</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="2" t="n">
         <v>1062600</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="2" t="n">
         <v>177100</v>
       </c>
-      <c r="J28" s="0" t="n">
+      <c r="J28" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K28" s="35" t="n">
+      <c r="K28" s="36" t="n">
         <v>1062600</v>
       </c>
-      <c r="L28" s="0" t="n">
+      <c r="L28" s="2" t="n">
         <f aca="false">L58</f>
         <v>0</v>
       </c>
-      <c r="M28" s="0" t="n">
+      <c r="M28" s="2" t="n">
         <f aca="false">M58</f>
         <v>0</v>
       </c>
-      <c r="N28" s="0" t="n">
+      <c r="N28" s="2" t="n">
         <f aca="false">N58</f>
         <v>0</v>
       </c>
-      <c r="O28" s="35" t="n">
+      <c r="O28" s="36" t="n">
         <v>1062600</v>
       </c>
-      <c r="P28" s="35" t="n">
+      <c r="P28" s="36" t="n">
         <v>177100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="36" t="n">
+      <c r="B29" s="23" t="n">
         <f aca="false">SUM(B3:B28)</f>
         <v>3946800</v>
       </c>
@@ -4625,693 +4703,694 @@
         <f aca="false">SUM(E3:E28)</f>
         <v>22365200</v>
       </c>
-      <c r="F29" s="36" t="n">
+      <c r="F29" s="23" t="n">
         <f aca="false">SUM(F3:F28)</f>
         <v>13156000</v>
       </c>
-      <c r="G29" s="36" t="n">
+      <c r="G29" s="23" t="n">
         <f aca="false">SUM(G3:G28)</f>
         <v>3946800</v>
       </c>
-      <c r="H29" s="36" t="n">
+      <c r="H29" s="23" t="n">
         <f aca="false">SUM(B29:G29)</f>
         <v>78936000</v>
       </c>
-      <c r="K29" s="35" t="n">
+      <c r="K29" s="36" t="n">
         <f aca="false">SUM(K3:K28)</f>
         <v>3946800</v>
       </c>
-      <c r="L29" s="0" t="n">
+      <c r="L29" s="2" t="n">
         <f aca="false">SUM(L3:L28)</f>
         <v>1932414</v>
       </c>
-      <c r="M29" s="0" t="n">
+      <c r="M29" s="2" t="n">
         <f aca="false">SUM(M3:M28)</f>
         <v>2057396</v>
       </c>
-      <c r="N29" s="0" t="n">
+      <c r="N29" s="2" t="n">
         <f aca="false">SUM(N3:N28)</f>
         <v>1973400</v>
       </c>
-      <c r="O29" s="35" t="n">
+      <c r="O29" s="36" t="n">
         <f aca="false">SUM(O3:O28)</f>
         <v>13156000</v>
       </c>
-      <c r="P29" s="35" t="n">
+      <c r="P29" s="36" t="n">
         <f aca="false">SUM(P3:P28)</f>
         <v>3946800</v>
       </c>
-      <c r="Q29" s="0" t="n">
+      <c r="Q29" s="2" t="n">
         <f aca="false">SUM(K29:P29)</f>
         <v>27012810</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K30" s="0" t="n">
+      <c r="K30" s="2" t="n">
         <f aca="false">COMBIN(26,G2)*COMBIN(G2-1,K2-1)</f>
         <v>3946800</v>
       </c>
-      <c r="L30" s="0" t="n">
+      <c r="L30" s="2" t="n">
         <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,L2-1)</f>
         <v>9867000</v>
       </c>
-      <c r="M30" s="0" t="n">
+      <c r="M30" s="2" t="n">
         <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,M2-1)</f>
         <v>13156000</v>
       </c>
-      <c r="N30" s="0" t="n">
+      <c r="N30" s="2" t="n">
         <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,N2-1)</f>
         <v>9867000</v>
       </c>
-      <c r="O30" s="0" t="n">
+      <c r="O30" s="2" t="n">
         <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,O2-1)</f>
         <v>3946800</v>
       </c>
-      <c r="P30" s="0" t="n">
+      <c r="P30" s="2" t="n">
         <f aca="false">COMBIN(26,$G$2)*COMBIN($G$2-1,P2-1)</f>
         <v>657800</v>
       </c>
-      <c r="Q30" s="0" t="n">
+      <c r="Q30" s="2" t="n">
         <f aca="false">SUM(K30:P30)</f>
         <v>41441400</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="n">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="2" t="n">
         <v>1330</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="2" t="n">
         <v>1540</v>
       </c>
-      <c r="F33" s="0" t="n">
+      <c r="F33" s="2" t="n">
         <f aca="false">B33*C33+D33*E33</f>
         <v>17220</v>
       </c>
-      <c r="J33" s="0" t="n">
+      <c r="J33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="0" t="n">
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="n">
         <v>42504</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J35" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="0" t="n">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="n">
         <v>17710</v>
       </c>
-      <c r="P35" s="0" t="n">
+      <c r="P35" s="2" t="n">
         <v>76153</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J36" s="0" t="n">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="0" t="n">
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="n">
         <v>4620</v>
       </c>
-      <c r="O36" s="0" t="n">
+      <c r="O36" s="2" t="n">
         <v>48510</v>
       </c>
-      <c r="P36" s="0" t="n">
+      <c r="P36" s="2" t="n">
         <v>102487</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J37" s="0" t="n">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="0" t="n">
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2" t="n">
         <v>15960</v>
       </c>
-      <c r="O37" s="0" t="n">
+      <c r="O37" s="2" t="n">
         <v>88620</v>
       </c>
-      <c r="P37" s="0" t="n">
+      <c r="P37" s="2" t="n">
         <v>122836</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J38" s="0" t="n">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J38" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="0" t="n">
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="N38" s="0" t="n">
+      <c r="N38" s="2" t="n">
         <v>34200</v>
       </c>
-      <c r="O38" s="0" t="n">
+      <c r="O38" s="2" t="n">
         <v>135000</v>
       </c>
-      <c r="P38" s="0" t="n">
+      <c r="P38" s="2" t="n">
         <v>138340</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J39" s="0" t="n">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="0" t="n">
+      <c r="K39" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="L39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="0" t="n">
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="n">
         <v>4104</v>
       </c>
-      <c r="N39" s="0" t="n">
+      <c r="N39" s="2" t="n">
         <v>58140</v>
       </c>
-      <c r="O39" s="0" t="n">
+      <c r="O39" s="2" t="n">
         <v>185256</v>
       </c>
-      <c r="P39" s="0" t="n">
+      <c r="P39" s="2" t="n">
         <v>149968</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J40" s="0" t="n">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J40" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K40" s="0" t="n">
+      <c r="K40" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="L40" s="0" t="n">
+      <c r="L40" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="M40" s="0" t="n">
+      <c r="M40" s="2" t="n">
         <v>10710</v>
       </c>
-      <c r="N40" s="0" t="n">
+      <c r="N40" s="2" t="n">
         <v>85680</v>
       </c>
-      <c r="O40" s="0" t="n">
+      <c r="O40" s="2" t="n">
         <v>237552</v>
       </c>
-      <c r="P40" s="0" t="n">
+      <c r="P40" s="2" t="n">
         <v>158536</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J41" s="0" t="n">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J41" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K41" s="0" t="n">
+      <c r="K41" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="L41" s="0" t="n">
+      <c r="L41" s="2" t="n">
         <v>680</v>
       </c>
-      <c r="M41" s="0" t="n">
+      <c r="M41" s="2" t="n">
         <v>21760</v>
       </c>
-      <c r="N41" s="0" t="n">
+      <c r="N41" s="2" t="n">
         <v>114240</v>
       </c>
-      <c r="O41" s="0" t="n">
+      <c r="O41" s="2" t="n">
         <v>290528</v>
       </c>
-      <c r="P41" s="0" t="n">
+      <c r="P41" s="2" t="n">
         <v>164724</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J42" s="0" t="n">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J42" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K42" s="0" t="n">
+      <c r="K42" s="2" t="n">
         <v>504</v>
       </c>
-      <c r="L42" s="0" t="n">
+      <c r="L42" s="2" t="n">
         <v>2160</v>
       </c>
-      <c r="M42" s="0" t="n">
+      <c r="M42" s="2" t="n">
         <v>37800</v>
       </c>
-      <c r="N42" s="0" t="n">
+      <c r="N42" s="2" t="n">
         <v>141120</v>
       </c>
-      <c r="O42" s="0" t="n">
+      <c r="O42" s="2" t="n">
         <v>343224</v>
       </c>
-      <c r="P42" s="0" t="n">
+      <c r="P42" s="2" t="n">
         <v>169092</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J43" s="0" t="n">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J43" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K43" s="0" t="n">
+      <c r="K43" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="L43" s="0" t="n">
+      <c r="L43" s="2" t="n">
         <v>5250</v>
       </c>
-      <c r="M43" s="0" t="n">
+      <c r="M43" s="2" t="n">
         <v>58800</v>
       </c>
-      <c r="N43" s="0" t="n">
+      <c r="N43" s="2" t="n">
         <v>163800</v>
       </c>
-      <c r="O43" s="0" t="n">
+      <c r="O43" s="2" t="n">
         <v>395010</v>
       </c>
-      <c r="P43" s="0" t="n">
+      <c r="P43" s="2" t="n">
         <v>172095</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J44" s="0" t="n">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J44" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K44" s="0" t="n">
+      <c r="K44" s="2" t="n">
         <v>2772</v>
       </c>
-      <c r="L44" s="0" t="n">
+      <c r="L44" s="2" t="n">
         <v>10780</v>
       </c>
-      <c r="M44" s="0" t="n">
+      <c r="M44" s="2" t="n">
         <v>84084</v>
       </c>
-      <c r="N44" s="0" t="n">
+      <c r="N44" s="2" t="n">
         <v>180180</v>
       </c>
-      <c r="O44" s="0" t="n">
+      <c r="O44" s="2" t="n">
         <v>445522</v>
       </c>
-      <c r="P44" s="0" t="n">
+      <c r="P44" s="2" t="n">
         <v>174097</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J45" s="0" t="n">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K45" s="0" t="n">
+      <c r="K45" s="2" t="n">
         <v>5544</v>
       </c>
-      <c r="L45" s="0" t="n">
+      <c r="L45" s="2" t="n">
         <v>19656</v>
       </c>
-      <c r="M45" s="0" t="n">
+      <c r="M45" s="2" t="n">
         <v>112320</v>
       </c>
-      <c r="N45" s="0" t="n">
+      <c r="N45" s="2" t="n">
         <v>188760</v>
       </c>
-      <c r="O45" s="0" t="n">
+      <c r="O45" s="2" t="n">
         <v>494604</v>
       </c>
-      <c r="P45" s="0" t="n">
+      <c r="P45" s="2" t="n">
         <v>175384</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J46" s="0" t="n">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J46" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="K46" s="0" t="n">
+      <c r="K46" s="2" t="n">
         <v>10296</v>
       </c>
-      <c r="L46" s="0" t="n">
+      <c r="L46" s="2" t="n">
         <v>32760</v>
       </c>
-      <c r="M46" s="0" t="n">
+      <c r="M46" s="2" t="n">
         <v>141570</v>
       </c>
-      <c r="N46" s="0" t="n">
+      <c r="N46" s="2" t="n">
         <v>188760</v>
       </c>
-      <c r="O46" s="0" t="n">
+      <c r="O46" s="2" t="n">
         <v>542256</v>
       </c>
-      <c r="P46" s="0" t="n">
+      <c r="P46" s="2" t="n">
         <v>176176</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J47" s="0" t="n">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J47" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K47" s="0" t="n">
+      <c r="K47" s="2" t="n">
         <v>18018</v>
       </c>
-      <c r="L47" s="0" t="n">
+      <c r="L47" s="2" t="n">
         <v>50820</v>
       </c>
-      <c r="M47" s="0" t="n">
+      <c r="M47" s="2" t="n">
         <v>169400</v>
       </c>
-      <c r="N47" s="0" t="n">
+      <c r="N47" s="2" t="n">
         <v>180180</v>
       </c>
-      <c r="O47" s="0" t="n">
+      <c r="O47" s="2" t="n">
         <v>588588</v>
       </c>
-      <c r="P47" s="0" t="n">
+      <c r="P47" s="2" t="n">
         <v>176638</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J48" s="0" t="n">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J48" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="K48" s="0" t="n">
+      <c r="K48" s="2" t="n">
         <v>30030</v>
       </c>
-      <c r="L48" s="0" t="n">
+      <c r="L48" s="2" t="n">
         <v>74250</v>
       </c>
-      <c r="M48" s="0" t="n">
+      <c r="M48" s="2" t="n">
         <v>193050</v>
       </c>
-      <c r="N48" s="0" t="n">
+      <c r="N48" s="2" t="n">
         <v>163800</v>
       </c>
-      <c r="O48" s="0" t="n">
+      <c r="O48" s="2" t="n">
         <v>633780</v>
       </c>
-      <c r="P48" s="0" t="n">
+      <c r="P48" s="2" t="n">
         <v>176890</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J49" s="0" t="n">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J49" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K49" s="0" t="n">
+      <c r="K49" s="2" t="n">
         <v>48048</v>
       </c>
-      <c r="L49" s="0" t="n">
+      <c r="L49" s="2" t="n">
         <v>102960</v>
       </c>
-      <c r="M49" s="0" t="n">
+      <c r="M49" s="2" t="n">
         <v>209664</v>
       </c>
-      <c r="N49" s="0" t="n">
+      <c r="N49" s="2" t="n">
         <v>141120</v>
       </c>
-      <c r="O49" s="0" t="n">
+      <c r="O49" s="2" t="n">
         <v>678048</v>
       </c>
-      <c r="P49" s="0" t="n">
+      <c r="P49" s="2" t="n">
         <v>177016</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J50" s="0" t="n">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J50" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K50" s="0" t="n">
+      <c r="K50" s="2" t="n">
         <v>74256</v>
       </c>
-      <c r="L50" s="0" t="n">
+      <c r="L50" s="2" t="n">
         <v>136136</v>
       </c>
-      <c r="M50" s="0" t="n">
+      <c r="M50" s="2" t="n">
         <v>216580</v>
       </c>
-      <c r="N50" s="0" t="n">
+      <c r="N50" s="2" t="n">
         <v>114240</v>
       </c>
-      <c r="O50" s="0" t="n">
+      <c r="O50" s="2" t="n">
         <v>721616</v>
       </c>
-      <c r="P50" s="0" t="n">
+      <c r="P50" s="2" t="n">
         <v>177072</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J51" s="0" t="n">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J51" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="K51" s="0" t="n">
+      <c r="K51" s="2" t="n">
         <v>111384</v>
       </c>
-      <c r="L51" s="0" t="n">
+      <c r="L51" s="2" t="n">
         <v>171990</v>
       </c>
-      <c r="M51" s="0" t="n">
+      <c r="M51" s="2" t="n">
         <v>211680</v>
       </c>
-      <c r="N51" s="0" t="n">
+      <c r="N51" s="2" t="n">
         <v>85680</v>
       </c>
-      <c r="O51" s="0" t="n">
+      <c r="O51" s="2" t="n">
         <v>764694</v>
       </c>
-      <c r="P51" s="0" t="n">
+      <c r="P51" s="2" t="n">
         <v>177093</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J52" s="0" t="n">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J52" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K52" s="0" t="n">
+      <c r="K52" s="2" t="n">
         <v>162792</v>
       </c>
-      <c r="L52" s="0" t="n">
+      <c r="L52" s="2" t="n">
         <v>207480</v>
       </c>
-      <c r="M52" s="0" t="n">
+      <c r="M52" s="2" t="n">
         <v>193800</v>
       </c>
-      <c r="N52" s="0" t="n">
+      <c r="N52" s="2" t="n">
         <v>58140</v>
       </c>
-      <c r="O52" s="0" t="n">
+      <c r="O52" s="2" t="n">
         <v>807462</v>
       </c>
-      <c r="P52" s="0" t="n">
+      <c r="P52" s="2" t="n">
         <v>177099</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J53" s="0" t="n">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J53" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="K53" s="0" t="n">
+      <c r="K53" s="2" t="n">
         <v>232560</v>
       </c>
-      <c r="L53" s="0" t="n">
+      <c r="L53" s="2" t="n">
         <v>238000</v>
       </c>
-      <c r="M53" s="0" t="n">
+      <c r="M53" s="2" t="n">
         <v>163200</v>
       </c>
-      <c r="N53" s="0" t="n">
+      <c r="N53" s="2" t="n">
         <v>34200</v>
       </c>
-      <c r="O53" s="0" t="n">
+      <c r="O53" s="2" t="n">
         <v>850060</v>
       </c>
-      <c r="P53" s="0" t="n">
+      <c r="P53" s="2" t="n">
         <v>177100</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J54" s="0" t="n">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J54" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="K54" s="0" t="n">
+      <c r="K54" s="2" t="n">
         <v>325584</v>
       </c>
-      <c r="L54" s="0" t="n">
+      <c r="L54" s="2" t="n">
         <v>257040</v>
       </c>
-      <c r="M54" s="0" t="n">
+      <c r="M54" s="2" t="n">
         <v>122094</v>
       </c>
-      <c r="N54" s="0" t="n">
+      <c r="N54" s="2" t="n">
         <v>15960</v>
       </c>
-      <c r="O54" s="0" t="n">
+      <c r="O54" s="2" t="n">
         <v>892584</v>
       </c>
-      <c r="P54" s="0" t="n">
+      <c r="P54" s="2" t="n">
         <v>177100</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J55" s="0" t="n">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J55" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="K55" s="0" t="n">
+      <c r="K55" s="2" t="n">
         <v>447678</v>
       </c>
-      <c r="L55" s="0" t="n">
+      <c r="L55" s="2" t="n">
         <v>255816</v>
       </c>
-      <c r="M55" s="0" t="n">
+      <c r="M55" s="2" t="n">
         <v>75240</v>
       </c>
-      <c r="N55" s="0" t="n">
+      <c r="N55" s="2" t="n">
         <v>4620</v>
       </c>
-      <c r="O55" s="0" t="n">
+      <c r="O55" s="2" t="n">
         <v>935088</v>
       </c>
-      <c r="P55" s="0" t="n">
+      <c r="P55" s="2" t="n">
         <v>177100</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J56" s="0" t="n">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J56" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K56" s="0" t="n">
+      <c r="K56" s="2" t="n">
         <v>605682</v>
       </c>
-      <c r="L56" s="0" t="n">
+      <c r="L56" s="2" t="n">
         <v>222870</v>
       </c>
-      <c r="M56" s="0" t="n">
+      <c r="M56" s="2" t="n">
         <v>30590</v>
       </c>
-      <c r="N56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="0" t="n">
+      <c r="N56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="n">
         <v>977592</v>
       </c>
-      <c r="P56" s="0" t="n">
+      <c r="P56" s="2" t="n">
         <v>177100</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J57" s="0" t="n">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J57" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="K57" s="0" t="n">
+      <c r="K57" s="2" t="n">
         <v>807576</v>
       </c>
-      <c r="L57" s="0" t="n">
+      <c r="L57" s="2" t="n">
         <v>143640</v>
       </c>
-      <c r="M57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="0" t="n">
+      <c r="M57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="n">
         <v>1020096</v>
       </c>
-      <c r="P57" s="0" t="n">
+      <c r="P57" s="2" t="n">
         <v>177100</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J58" s="0" t="n">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J58" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K58" s="0" t="n">
+      <c r="K58" s="2" t="n">
         <v>1062600</v>
       </c>
-      <c r="L58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="0" t="n">
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2" t="n">
         <v>1062600</v>
       </c>
-      <c r="P58" s="0" t="n">
+      <c r="P58" s="2" t="n">
         <v>177100</v>
       </c>
     </row>
@@ -5327,24 +5406,24 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AK54"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="4.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="5.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="5.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="18" style="0" width="5.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="2" width="4.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="5.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="5.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="1.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="18" style="2" width="5.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23"/>
+      <c r="A1" s="24"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="23"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="38"/>
       <c r="E1" s="39"/>
       <c r="F1" s="38"/>
@@ -5355,11 +5434,11 @@
       <c r="K1" s="39"/>
       <c r="L1" s="38"/>
       <c r="M1" s="39"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="Z1" s="0" t="n">
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="Z1" s="2" t="n">
         <f aca="false">COMBIN(AA1,AB1)</f>
         <v>190</v>
       </c>
@@ -5369,33 +5448,33 @@
       <c r="AB1" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC1" s="0" t="n">
+      <c r="AC1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD1" s="0" t="n">
+      <c r="AD1" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE1" s="0" t="n">
+      <c r="AE1" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AF1" s="40"/>
       <c r="AG1" s="40"/>
-      <c r="AH1" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ1" s="0" t="n">
+      <c r="AH1" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
         <f aca="false">Z1*AH1</f>
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="n">
+      <c r="A2" s="24" t="n">
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="38"/>
       <c r="E2" s="39"/>
       <c r="F2" s="38"/>
@@ -5410,17 +5489,17 @@
       </c>
       <c r="L2" s="38"/>
       <c r="M2" s="39"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="V2" s="0" t="s">
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="V2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="W2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z2" s="0" t="n">
+      <c r="W2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="2" t="n">
         <f aca="false">COMBIN(AA2,AB2)</f>
         <v>190</v>
       </c>
@@ -5430,13 +5509,13 @@
       <c r="AB2" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC2" s="0" t="n">
+      <c r="AC2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD2" s="0" t="n">
+      <c r="AD2" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE2" s="0" t="n">
+      <c r="AE2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AF2" s="40" t="n">
@@ -5445,19 +5524,19 @@
       <c r="AG2" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH2" s="0" t="n">
+      <c r="AH2" s="2" t="n">
         <f aca="false">COMBIN(AF2,AG2)</f>
         <v>3</v>
       </c>
-      <c r="AJ2" s="0" t="n">
+      <c r="AJ2" s="2" t="n">
         <f aca="false">Z2*AH2</f>
         <v>570</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="39"/>
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
@@ -5474,17 +5553,17 @@
         <v>6</v>
       </c>
       <c r="M3" s="39"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="V3" s="0" t="s">
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="V3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="W3" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z3" s="0" t="n">
+      <c r="W3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="2" t="n">
         <f aca="false">COMBIN(AA3,AB3)</f>
         <v>190</v>
       </c>
@@ -5494,13 +5573,13 @@
       <c r="AB3" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC3" s="0" t="n">
+      <c r="AC3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD3" s="0" t="n">
+      <c r="AD3" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE3" s="0" t="n">
+      <c r="AE3" s="2" t="n">
         <v>5</v>
       </c>
       <c r="AF3" s="40" t="n">
@@ -5509,23 +5588,23 @@
       <c r="AG3" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH3" s="0" t="n">
+      <c r="AH3" s="2" t="n">
         <f aca="false">COMBIN(AF3,AG3)</f>
         <v>3</v>
       </c>
-      <c r="AJ3" s="0" t="n">
+      <c r="AJ3" s="2" t="n">
         <f aca="false">Z3*AH3</f>
         <v>570</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" s="23" t="n">
+      <c r="A4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C4" s="23" t="n">
+      <c r="C4" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D4" s="39"/>
@@ -5542,15 +5621,15 @@
         <v>6</v>
       </c>
       <c r="M4" s="39"/>
-      <c r="N4" s="23" t="n">
+      <c r="N4" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23" t="n">
+      <c r="O4" s="24"/>
+      <c r="P4" s="24" t="n">
         <v>1026</v>
       </c>
-      <c r="Q4" s="23"/>
-      <c r="Z4" s="0" t="n">
+      <c r="Q4" s="24"/>
+      <c r="Z4" s="2" t="n">
         <f aca="false">COMBIN(AA4,AB4)</f>
         <v>190</v>
       </c>
@@ -5560,13 +5639,13 @@
       <c r="AB4" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC4" s="0" t="n">
+      <c r="AC4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD4" s="0" t="n">
+      <c r="AD4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE4" s="0" t="n">
+      <c r="AE4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="AF4" s="40" t="n">
@@ -5575,23 +5654,23 @@
       <c r="AG4" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH4" s="0" t="n">
+      <c r="AH4" s="2" t="n">
         <f aca="false">COMBIN(AF4,AG4)</f>
         <v>6</v>
       </c>
-      <c r="AJ4" s="0" t="n">
+      <c r="AJ4" s="2" t="n">
         <f aca="false">Z4*AH4</f>
         <v>1140</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="n">
+      <c r="A5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="24" t="n">
         <v>190</v>
       </c>
       <c r="D5" s="39"/>
@@ -5608,15 +5687,15 @@
         <v>6</v>
       </c>
       <c r="M5" s="39"/>
-      <c r="N5" s="23" t="n">
+      <c r="N5" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23" t="n">
+      <c r="O5" s="24"/>
+      <c r="P5" s="24" t="n">
         <v>1140</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="Z5" s="0" t="n">
+      <c r="Q5" s="24"/>
+      <c r="Z5" s="2" t="n">
         <f aca="false">COMBIN(AA5,AB5)</f>
         <v>190</v>
       </c>
@@ -5626,33 +5705,33 @@
       <c r="AB5" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" s="0" t="n">
+      <c r="AC5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE5" s="0" t="n">
+      <c r="AE5" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AF5" s="40"/>
       <c r="AG5" s="40"/>
-      <c r="AH5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="0" t="n">
+      <c r="AH5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="2" t="n">
         <f aca="false">Z5*AH5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="A6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <v>210</v>
       </c>
       <c r="D6" s="39"/>
@@ -5669,15 +5748,15 @@
         <v>6</v>
       </c>
       <c r="M6" s="39"/>
-      <c r="N6" s="23" t="n">
+      <c r="N6" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23" t="n">
+      <c r="O6" s="24"/>
+      <c r="P6" s="24" t="n">
         <v>1260</v>
       </c>
-      <c r="Q6" s="23"/>
-      <c r="Z6" s="0" t="n">
+      <c r="Q6" s="24"/>
+      <c r="Z6" s="2" t="n">
         <f aca="false">COMBIN(AA6,AB6)</f>
         <v>190</v>
       </c>
@@ -5687,13 +5766,13 @@
       <c r="AB6" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="0" t="n">
+      <c r="AC6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE6" s="0" t="n">
+      <c r="AE6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AF6" s="40" t="n">
@@ -5702,23 +5781,23 @@
       <c r="AG6" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH6" s="0" t="n">
+      <c r="AH6" s="2" t="n">
         <f aca="false">COMBIN(AF6,AG6)</f>
         <v>1</v>
       </c>
-      <c r="AJ6" s="0" t="n">
+      <c r="AJ6" s="2" t="n">
         <f aca="false">Z6*AH6</f>
         <v>190</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="23" t="n">
+      <c r="A7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="39"/>
@@ -5735,15 +5814,15 @@
         <v>6</v>
       </c>
       <c r="M7" s="39"/>
-      <c r="N7" s="23" t="n">
+      <c r="N7" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23" t="n">
+      <c r="O7" s="24"/>
+      <c r="P7" s="24" t="n">
         <v>1386</v>
       </c>
-      <c r="Q7" s="23"/>
-      <c r="Z7" s="0" t="n">
+      <c r="Q7" s="24"/>
+      <c r="Z7" s="2" t="n">
         <f aca="false">COMBIN(AA7,AB7)</f>
         <v>190</v>
       </c>
@@ -5753,13 +5832,13 @@
       <c r="AB7" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="0" t="n">
+      <c r="AC7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE7" s="0" t="n">
+      <c r="AE7" s="2" t="n">
         <v>5</v>
       </c>
       <c r="AF7" s="40" t="n">
@@ -5768,23 +5847,23 @@
       <c r="AG7" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH7" s="0" t="n">
+      <c r="AH7" s="2" t="n">
         <f aca="false">COMBIN(AF7,AG7)</f>
         <v>3</v>
       </c>
-      <c r="AJ7" s="0" t="n">
+      <c r="AJ7" s="2" t="n">
         <f aca="false">Z7*AH7</f>
         <v>570</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="23" t="n">
+      <c r="A8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <v>231</v>
       </c>
       <c r="D8" s="39"/>
@@ -5801,15 +5880,15 @@
         <v>6</v>
       </c>
       <c r="M8" s="39"/>
-      <c r="N8" s="23" t="n">
+      <c r="N8" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23" t="n">
+      <c r="O8" s="24"/>
+      <c r="P8" s="24" t="n">
         <v>1386</v>
       </c>
-      <c r="Q8" s="23"/>
-      <c r="Z8" s="0" t="n">
+      <c r="Q8" s="24"/>
+      <c r="Z8" s="2" t="n">
         <f aca="false">COMBIN(AA8,AB8)</f>
         <v>171</v>
       </c>
@@ -5819,13 +5898,13 @@
       <c r="AB8" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC8" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="0" t="n">
+      <c r="AC8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AE8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="AF8" s="40" t="n">
@@ -5834,23 +5913,23 @@
       <c r="AG8" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH8" s="0" t="n">
+      <c r="AH8" s="2" t="n">
         <f aca="false">COMBIN(AF8,AG8)</f>
         <v>6</v>
       </c>
-      <c r="AJ8" s="0" t="n">
+      <c r="AJ8" s="2" t="n">
         <f aca="false">Z8*AH8</f>
         <v>1026</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B9" s="23" t="n">
+      <c r="A9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D9" s="39"/>
@@ -5867,15 +5946,15 @@
         <v>5</v>
       </c>
       <c r="M9" s="39"/>
-      <c r="N9" s="23" t="n">
+      <c r="N9" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23" t="n">
+      <c r="O9" s="24"/>
+      <c r="P9" s="24" t="n">
         <v>1026</v>
       </c>
-      <c r="Q9" s="23"/>
-      <c r="Z9" s="0" t="n">
+      <c r="Q9" s="24"/>
+      <c r="Z9" s="2" t="n">
         <f aca="false">COMBIN(AA9,AB9)</f>
         <v>190</v>
       </c>
@@ -5885,13 +5964,13 @@
       <c r="AB9" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD9" s="0" t="n">
+      <c r="AC9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE9" s="0" t="n">
+      <c r="AE9" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AF9" s="40" t="n">
@@ -5900,21 +5979,21 @@
       <c r="AG9" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH9" s="0" t="n">
+      <c r="AH9" s="2" t="n">
         <f aca="false">COMBIN(AF9,AG9)</f>
         <v>1</v>
       </c>
-      <c r="AJ9" s="0" t="n">
+      <c r="AJ9" s="2" t="n">
         <f aca="false">Z9*AH9</f>
         <v>190</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23" t="n">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D10" s="39"/>
@@ -5933,15 +6012,15 @@
         <v>5</v>
       </c>
       <c r="M10" s="39"/>
-      <c r="N10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="23"/>
-      <c r="Z10" s="0" t="n">
+      <c r="N10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="24"/>
+      <c r="Z10" s="2" t="n">
         <f aca="false">COMBIN(AA10,AB10)</f>
         <v>190</v>
       </c>
@@ -5951,13 +6030,13 @@
       <c r="AB10" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC10" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" s="0" t="n">
+      <c r="AC10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE10" s="0" t="n">
+      <c r="AE10" s="2" t="n">
         <v>5</v>
       </c>
       <c r="AF10" s="40" t="n">
@@ -5966,23 +6045,23 @@
       <c r="AG10" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH10" s="0" t="n">
+      <c r="AH10" s="2" t="n">
         <f aca="false">COMBIN(AF10,AG10)</f>
         <v>3</v>
       </c>
-      <c r="AJ10" s="0" t="n">
+      <c r="AJ10" s="2" t="n">
         <f aca="false">Z10*AH10</f>
         <v>570</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="24" t="n">
         <v>190</v>
       </c>
       <c r="D11" s="39"/>
@@ -5999,15 +6078,15 @@
         <v>5</v>
       </c>
       <c r="M11" s="39"/>
-      <c r="N11" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23" t="n">
+      <c r="N11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24" t="n">
         <v>570</v>
       </c>
-      <c r="Q11" s="23"/>
-      <c r="Z11" s="0" t="n">
+      <c r="Q11" s="24"/>
+      <c r="Z11" s="2" t="n">
         <f aca="false">COMBIN(AA11,AB11)</f>
         <v>153</v>
       </c>
@@ -6017,13 +6096,13 @@
       <c r="AB11" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC11" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD11" s="0" t="n">
+      <c r="AC11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD11" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE11" s="0" t="n">
+      <c r="AE11" s="2" t="n">
         <v>6</v>
       </c>
       <c r="AF11" s="40" t="n">
@@ -6032,23 +6111,23 @@
       <c r="AG11" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH11" s="0" t="n">
+      <c r="AH11" s="2" t="n">
         <f aca="false">COMBIN(AF11,AG11)</f>
         <v>6</v>
       </c>
-      <c r="AJ11" s="0" t="n">
+      <c r="AJ11" s="2" t="n">
         <f aca="false">Z11*AH11</f>
         <v>918</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="23" t="n">
+      <c r="A12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="24" t="n">
         <v>210</v>
       </c>
       <c r="D12" s="39"/>
@@ -6065,15 +6144,15 @@
         <v>5</v>
       </c>
       <c r="M12" s="39"/>
-      <c r="N12" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23" t="n">
+      <c r="N12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24" t="n">
         <v>630</v>
       </c>
-      <c r="Q12" s="23"/>
-      <c r="Z12" s="0" t="n">
+      <c r="Q12" s="24"/>
+      <c r="Z12" s="2" t="n">
         <f aca="false">COMBIN(AA12,AB12)</f>
         <v>190</v>
       </c>
@@ -6083,34 +6162,34 @@
       <c r="AB12" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC12" s="0" t="n">
+      <c r="AC12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD12" s="0" t="n">
+      <c r="AD12" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE12" s="0" t="n">
+      <c r="AE12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AF12" s="40"/>
       <c r="AG12" s="40"/>
-      <c r="AH12" s="0" t="n">
+      <c r="AH12" s="2" t="n">
         <f aca="false">COMBIN(AF12,AG12)</f>
         <v>1</v>
       </c>
-      <c r="AJ12" s="0" t="n">
+      <c r="AJ12" s="2" t="n">
         <f aca="false">Z12*AH12</f>
         <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="23" t="n">
+      <c r="A13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="24" t="n">
         <v>231</v>
       </c>
       <c r="D13" s="39"/>
@@ -6127,15 +6206,15 @@
         <v>5</v>
       </c>
       <c r="M13" s="39"/>
-      <c r="N13" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23" t="n">
+      <c r="N13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24" t="n">
         <v>693</v>
       </c>
-      <c r="Q13" s="23"/>
-      <c r="Z13" s="0" t="n">
+      <c r="Q13" s="24"/>
+      <c r="Z13" s="2" t="n">
         <f aca="false">COMBIN(AA13,AB13)</f>
         <v>190</v>
       </c>
@@ -6145,13 +6224,13 @@
       <c r="AB13" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC13" s="0" t="n">
+      <c r="AC13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD13" s="0" t="n">
+      <c r="AD13" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE13" s="0" t="n">
+      <c r="AE13" s="2" t="n">
         <v>5</v>
       </c>
       <c r="AF13" s="40" t="n">
@@ -6160,23 +6239,23 @@
       <c r="AG13" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH13" s="0" t="n">
+      <c r="AH13" s="2" t="n">
         <f aca="false">COMBIN(AF13,AG13)</f>
         <v>3</v>
       </c>
-      <c r="AJ13" s="0" t="n">
+      <c r="AJ13" s="2" t="n">
         <f aca="false">Z13*AH13</f>
         <v>570</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="23" t="n">
+      <c r="A14" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="24" t="n">
         <v>231</v>
       </c>
       <c r="D14" s="39"/>
@@ -6193,15 +6272,15 @@
         <v>5</v>
       </c>
       <c r="M14" s="39"/>
-      <c r="N14" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23" t="n">
+      <c r="N14" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24" t="n">
         <v>693</v>
       </c>
-      <c r="Q14" s="23"/>
-      <c r="Z14" s="0" t="n">
+      <c r="Q14" s="24"/>
+      <c r="Z14" s="2" t="n">
         <f aca="false">COMBIN(AA14,AB14)</f>
         <v>153</v>
       </c>
@@ -6211,13 +6290,13 @@
       <c r="AB14" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC14" s="0" t="n">
+      <c r="AC14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AD14" s="0" t="n">
+      <c r="AD14" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE14" s="0" t="n">
+      <c r="AE14" s="2" t="n">
         <v>6</v>
       </c>
       <c r="AF14" s="40" t="n">
@@ -6226,23 +6305,23 @@
       <c r="AG14" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH14" s="0" t="n">
+      <c r="AH14" s="2" t="n">
         <f aca="false">COMBIN(AF14,AG14)</f>
         <v>6</v>
       </c>
-      <c r="AJ14" s="0" t="n">
+      <c r="AJ14" s="2" t="n">
         <f aca="false">Z14*AH14</f>
         <v>918</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="23" t="n">
+      <c r="A15" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="24" t="n">
         <v>231</v>
       </c>
       <c r="D15" s="39"/>
@@ -6259,15 +6338,15 @@
         <v>4</v>
       </c>
       <c r="M15" s="39"/>
-      <c r="N15" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23" t="n">
+      <c r="N15" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24" t="n">
         <v>693</v>
       </c>
-      <c r="Q15" s="23"/>
-      <c r="Z15" s="0" t="n">
+      <c r="Q15" s="24"/>
+      <c r="Z15" s="2" t="n">
         <f aca="false">COMBIN(AA15,AB15)</f>
         <v>190</v>
       </c>
@@ -6277,34 +6356,34 @@
       <c r="AB15" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC15" s="0" t="n">
+      <c r="AC15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AD15" s="0" t="n">
+      <c r="AD15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE15" s="0" t="n">
+      <c r="AE15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AF15" s="40"/>
       <c r="AG15" s="40"/>
-      <c r="AH15" s="0" t="n">
+      <c r="AH15" s="2" t="n">
         <f aca="false">COMBIN(AF15,AG15)</f>
         <v>1</v>
       </c>
-      <c r="AJ15" s="0" t="n">
+      <c r="AJ15" s="2" t="n">
         <f aca="false">Z15*AH15</f>
         <v>190</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B16" s="23" t="n">
+      <c r="A16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D16" s="39"/>
@@ -6321,15 +6400,15 @@
         <v>4</v>
       </c>
       <c r="M16" s="39"/>
-      <c r="N16" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23" t="n">
+      <c r="N16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24" t="n">
         <v>513</v>
       </c>
-      <c r="Q16" s="23"/>
-      <c r="Z16" s="0" t="n">
+      <c r="Q16" s="24"/>
+      <c r="Z16" s="2" t="n">
         <f aca="false">COMBIN(AA16,AB16)</f>
         <v>171</v>
       </c>
@@ -6339,13 +6418,13 @@
       <c r="AB16" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC16" s="0" t="n">
+      <c r="AC16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AD16" s="0" t="n">
+      <c r="AD16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE16" s="0" t="n">
+      <c r="AE16" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AF16" s="40" t="n">
@@ -6354,21 +6433,21 @@
       <c r="AG16" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH16" s="0" t="n">
+      <c r="AH16" s="2" t="n">
         <f aca="false">COMBIN(AF16,AG16)</f>
         <v>3</v>
       </c>
-      <c r="AJ16" s="0" t="n">
+      <c r="AJ16" s="2" t="n">
         <f aca="false">Z16*AH16</f>
         <v>513</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23" t="n">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D17" s="39"/>
@@ -6387,15 +6466,15 @@
         <v>4</v>
       </c>
       <c r="M17" s="39"/>
-      <c r="N17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="23"/>
-      <c r="Z17" s="0" t="n">
+      <c r="N17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="24"/>
+      <c r="Z17" s="2" t="n">
         <f aca="false">COMBIN(AA17,AB17)</f>
         <v>153</v>
       </c>
@@ -6405,13 +6484,13 @@
       <c r="AB17" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC17" s="0" t="n">
+      <c r="AC17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AD17" s="0" t="n">
+      <c r="AD17" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE17" s="0" t="n">
+      <c r="AE17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="AF17" s="40" t="n">
@@ -6420,23 +6499,23 @@
       <c r="AG17" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH17" s="0" t="n">
+      <c r="AH17" s="2" t="n">
         <f aca="false">COMBIN(AF17,AG17)</f>
         <v>6</v>
       </c>
-      <c r="AJ17" s="0" t="n">
+      <c r="AJ17" s="2" t="n">
         <f aca="false">Z17*AH17</f>
         <v>918</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B18" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="24" t="n">
         <v>190</v>
       </c>
       <c r="D18" s="39"/>
@@ -6453,15 +6532,15 @@
         <v>4</v>
       </c>
       <c r="M18" s="39"/>
-      <c r="N18" s="23" t="n">
+      <c r="N18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23" t="n">
+      <c r="O18" s="24"/>
+      <c r="P18" s="24" t="n">
         <v>190</v>
       </c>
-      <c r="Q18" s="23"/>
-      <c r="Z18" s="0" t="n">
+      <c r="Q18" s="24"/>
+      <c r="Z18" s="2" t="n">
         <f aca="false">COMBIN(AA18,AB18)</f>
         <v>153</v>
       </c>
@@ -6471,34 +6550,34 @@
       <c r="AB18" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC18" s="0" t="n">
+      <c r="AC18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AD18" s="0" t="n">
+      <c r="AD18" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE18" s="0" t="n">
+      <c r="AE18" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AF18" s="40"/>
       <c r="AG18" s="40"/>
-      <c r="AH18" s="0" t="n">
+      <c r="AH18" s="2" t="n">
         <f aca="false">COMBIN(AF18,AG18)</f>
         <v>1</v>
       </c>
-      <c r="AJ18" s="0" t="n">
+      <c r="AJ18" s="2" t="n">
         <f aca="false">Z18*AH18</f>
         <v>153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="23" t="n">
+      <c r="A19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C19" s="24" t="n">
         <v>210</v>
       </c>
       <c r="D19" s="39"/>
@@ -6515,15 +6594,15 @@
         <v>4</v>
       </c>
       <c r="M19" s="39"/>
-      <c r="N19" s="23" t="n">
+      <c r="N19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23" t="n">
+      <c r="O19" s="24"/>
+      <c r="P19" s="24" t="n">
         <v>210</v>
       </c>
-      <c r="Q19" s="23"/>
-      <c r="Z19" s="0" t="n">
+      <c r="Q19" s="24"/>
+      <c r="Z19" s="2" t="n">
         <f aca="false">COMBIN(AA19,AB19)</f>
         <v>153</v>
       </c>
@@ -6533,13 +6612,13 @@
       <c r="AB19" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC19" s="0" t="n">
+      <c r="AC19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AD19" s="0" t="n">
+      <c r="AD19" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE19" s="0" t="n">
+      <c r="AE19" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AF19" s="40" t="n">
@@ -6548,23 +6627,23 @@
       <c r="AG19" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH19" s="0" t="n">
+      <c r="AH19" s="2" t="n">
         <f aca="false">COMBIN(AF19,AG19)</f>
         <v>3</v>
       </c>
-      <c r="AJ19" s="0" t="n">
+      <c r="AJ19" s="2" t="n">
         <f aca="false">Z19*AH19</f>
         <v>459</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="23" t="n">
+      <c r="A20" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="24" t="n">
         <v>231</v>
       </c>
       <c r="D20" s="39"/>
@@ -6581,15 +6660,15 @@
         <v>4</v>
       </c>
       <c r="M20" s="39"/>
-      <c r="N20" s="23" t="n">
+      <c r="N20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23" t="n">
+      <c r="O20" s="24"/>
+      <c r="P20" s="24" t="n">
         <v>231</v>
       </c>
-      <c r="Q20" s="23"/>
-      <c r="Z20" s="0" t="n">
+      <c r="Q20" s="24"/>
+      <c r="Z20" s="2" t="n">
         <f aca="false">COMBIN(AA20,AB20)</f>
         <v>153</v>
       </c>
@@ -6599,13 +6678,13 @@
       <c r="AB20" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AC20" s="0" t="n">
+      <c r="AC20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AD20" s="0" t="n">
+      <c r="AD20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AE20" s="0" t="n">
+      <c r="AE20" s="2" t="n">
         <v>5</v>
       </c>
       <c r="AF20" s="40" t="n">
@@ -6614,23 +6693,23 @@
       <c r="AG20" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="AH20" s="0" t="n">
+      <c r="AH20" s="2" t="n">
         <f aca="false">COMBIN(AF20,AG20)</f>
         <v>6</v>
       </c>
-      <c r="AJ20" s="0" t="n">
+      <c r="AJ20" s="2" t="n">
         <f aca="false">Z20*AH20</f>
         <v>918</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="23" t="n">
+      <c r="A21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="24" t="n">
         <v>231</v>
       </c>
       <c r="D21" s="39"/>
@@ -6647,36 +6726,36 @@
         <v>3</v>
       </c>
       <c r="M21" s="39"/>
-      <c r="N21" s="23" t="n">
+      <c r="N21" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23" t="n">
+      <c r="O21" s="24"/>
+      <c r="P21" s="24" t="n">
         <v>231</v>
       </c>
-      <c r="Q21" s="23"/>
+      <c r="Q21" s="24"/>
       <c r="AA21" s="40"/>
       <c r="AB21" s="40"/>
-      <c r="AC21" s="23" t="s">
+      <c r="AC21" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD21" s="23" t="s">
+      <c r="AD21" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="AE21" s="23" t="s">
+      <c r="AE21" s="24" t="s">
         <v>11</v>
       </c>
       <c r="AF21" s="40"/>
       <c r="AG21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="23" t="n">
+      <c r="A22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C22" s="23" t="n">
+      <c r="C22" s="24" t="n">
         <v>231</v>
       </c>
       <c r="D22" s="39"/>
@@ -6693,37 +6772,37 @@
         <v>3</v>
       </c>
       <c r="M22" s="39"/>
-      <c r="N22" s="23" t="n">
+      <c r="N22" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23" t="n">
+      <c r="O22" s="24"/>
+      <c r="P22" s="24" t="n">
         <v>231</v>
       </c>
-      <c r="Q22" s="23"/>
-      <c r="AA22" s="41"/>
-      <c r="AB22" s="41"/>
-      <c r="AC22" s="41"/>
-      <c r="AD22" s="41"/>
-      <c r="AE22" s="41"/>
-      <c r="AF22" s="41"/>
-      <c r="AG22" s="41"/>
-      <c r="AJ22" s="0" t="n">
+      <c r="Q22" s="24"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="2"/>
+      <c r="AE22" s="2"/>
+      <c r="AF22" s="2"/>
+      <c r="AG22" s="2"/>
+      <c r="AJ22" s="2" t="n">
         <f aca="false">SUM(AJ2:AJ21)</f>
         <v>10573</v>
       </c>
-      <c r="AK22" s="21" t="n">
+      <c r="AK22" s="22" t="n">
         <v>11420</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B23" s="23" t="n">
+      <c r="A23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D23" s="39"/>
@@ -6740,32 +6819,32 @@
         <v>3</v>
       </c>
       <c r="M23" s="39"/>
-      <c r="N23" s="23" t="n">
+      <c r="N23" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23" t="n">
+      <c r="O23" s="24"/>
+      <c r="P23" s="24" t="n">
         <v>171</v>
       </c>
-      <c r="Q23" s="23"/>
-      <c r="AA23" s="41"/>
-      <c r="AB23" s="41"/>
-      <c r="AC23" s="41"/>
-      <c r="AD23" s="41"/>
-      <c r="AE23" s="41"/>
-      <c r="AF23" s="41"/>
-      <c r="AG23" s="41"/>
-      <c r="AJ23" s="0" t="n">
+      <c r="Q23" s="24"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AJ23" s="2" t="n">
         <f aca="false">AK22-AJ22</f>
         <v>847</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23" t="n">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D24" s="39"/>
@@ -6784,30 +6863,30 @@
         <v>3</v>
       </c>
       <c r="M24" s="39"/>
-      <c r="N24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="23"/>
-      <c r="AA24" s="41"/>
-      <c r="AB24" s="41"/>
-      <c r="AC24" s="41"/>
-      <c r="AD24" s="41"/>
-      <c r="AE24" s="41"/>
-      <c r="AF24" s="41"/>
-      <c r="AG24" s="41"/>
+      <c r="N24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="24"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="n">
+      <c r="A25" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C25" s="24" t="n">
         <v>190</v>
       </c>
       <c r="D25" s="39"/>
@@ -6824,30 +6903,30 @@
         <v>3</v>
       </c>
       <c r="M25" s="39"/>
-      <c r="N25" s="23" t="n">
+      <c r="N25" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23" t="n">
+      <c r="O25" s="24"/>
+      <c r="P25" s="24" t="n">
         <v>190</v>
       </c>
-      <c r="Q25" s="23"/>
-      <c r="AA25" s="41"/>
-      <c r="AB25" s="41"/>
-      <c r="AC25" s="41"/>
-      <c r="AD25" s="41"/>
-      <c r="AE25" s="41"/>
-      <c r="AF25" s="41"/>
-      <c r="AG25" s="41"/>
+      <c r="Q25" s="24"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AG25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="23" t="n">
+      <c r="A26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="C26" s="23" t="n">
+      <c r="C26" s="24" t="n">
         <v>210</v>
       </c>
       <c r="D26" s="39"/>
@@ -6864,28 +6943,28 @@
         <v>3</v>
       </c>
       <c r="M26" s="39"/>
-      <c r="N26" s="23" t="n">
+      <c r="N26" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23" t="n">
+      <c r="O26" s="24"/>
+      <c r="P26" s="24" t="n">
         <v>210</v>
       </c>
-      <c r="Q26" s="23"/>
-      <c r="AA26" s="41"/>
-      <c r="AB26" s="41"/>
-      <c r="AC26" s="41"/>
-      <c r="AD26" s="41"/>
-      <c r="AE26" s="41"/>
-      <c r="AF26" s="41"/>
-      <c r="AG26" s="41"/>
+      <c r="Q26" s="24"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23" t="n">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="C27" s="23" t="n">
+      <c r="C27" s="24" t="n">
         <v>136</v>
       </c>
       <c r="D27" s="39"/>
@@ -6902,28 +6981,28 @@
         <v>2</v>
       </c>
       <c r="M27" s="39"/>
-      <c r="N27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="23"/>
-      <c r="AA27" s="41"/>
-      <c r="AB27" s="41"/>
-      <c r="AC27" s="41"/>
-      <c r="AD27" s="41"/>
-      <c r="AE27" s="41"/>
-      <c r="AF27" s="41"/>
-      <c r="AG27" s="41"/>
+      <c r="N27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="24"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AG27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23" t="n">
+      <c r="A28" s="24"/>
+      <c r="B28" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="C28" s="23" t="n">
+      <c r="C28" s="24" t="n">
         <v>153</v>
       </c>
       <c r="D28" s="39"/>
@@ -6940,21 +7019,21 @@
         <v>2</v>
       </c>
       <c r="M28" s="39"/>
-      <c r="N28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="23"/>
+      <c r="N28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23" t="n">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C29" s="23" t="n">
+      <c r="C29" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D29" s="39"/>
@@ -6971,21 +7050,21 @@
         <v>2</v>
       </c>
       <c r="M29" s="39"/>
-      <c r="N29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="23"/>
+      <c r="N29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="24"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23" t="n">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C30" s="24" t="n">
         <v>190</v>
       </c>
       <c r="D30" s="39"/>
@@ -7002,21 +7081,21 @@
         <v>2</v>
       </c>
       <c r="M30" s="39"/>
-      <c r="N30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="23"/>
+      <c r="N30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="24"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23" t="n">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C31" s="24" t="n">
         <v>210</v>
       </c>
       <c r="D31" s="39"/>
@@ -7033,21 +7112,21 @@
         <v>2</v>
       </c>
       <c r="M31" s="39"/>
-      <c r="N31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="23"/>
+      <c r="N31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="24"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23" t="n">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="C32" s="23" t="n">
+      <c r="C32" s="24" t="n">
         <v>210</v>
       </c>
       <c r="D32" s="39"/>
@@ -7064,21 +7143,21 @@
         <v>2</v>
       </c>
       <c r="M32" s="39"/>
-      <c r="N32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="23"/>
+      <c r="N32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="24"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23" t="n">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="24" t="n">
         <v>136</v>
       </c>
       <c r="D33" s="39"/>
@@ -7095,21 +7174,21 @@
         <v>1</v>
       </c>
       <c r="M33" s="39"/>
-      <c r="N33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="23"/>
+      <c r="N33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="24"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23" t="n">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="24" t="n">
         <v>153</v>
       </c>
       <c r="D34" s="39"/>
@@ -7126,21 +7205,21 @@
         <v>1</v>
       </c>
       <c r="M34" s="39"/>
-      <c r="N34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="23"/>
+      <c r="N34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23" t="n">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="24" t="n">
         <v>171</v>
       </c>
       <c r="D35" s="39"/>
@@ -7157,21 +7236,21 @@
         <v>1</v>
       </c>
       <c r="M35" s="39"/>
-      <c r="N35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="23"/>
+      <c r="N35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23" t="n">
+      <c r="A36" s="24"/>
+      <c r="B36" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="C36" s="23" t="n">
+      <c r="C36" s="24" t="n">
         <v>190</v>
       </c>
       <c r="D36" s="39"/>
@@ -7188,21 +7267,21 @@
         <v>1</v>
       </c>
       <c r="M36" s="39"/>
-      <c r="N36" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="23"/>
+      <c r="N36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="24"/>
+      <c r="P36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="24"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23" t="n">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="C37" s="23" t="n">
+      <c r="C37" s="24" t="n">
         <v>210</v>
       </c>
       <c r="D37" s="39"/>
@@ -7219,21 +7298,21 @@
         <v>1</v>
       </c>
       <c r="M37" s="39"/>
-      <c r="N37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="23"/>
+      <c r="N37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="24"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23" t="n">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="C38" s="23" t="n">
+      <c r="C38" s="24" t="n">
         <v>231</v>
       </c>
       <c r="D38" s="39"/>
@@ -7250,19 +7329,19 @@
         <v>1</v>
       </c>
       <c r="M38" s="39"/>
-      <c r="N38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="23"/>
-      <c r="P38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="23"/>
+      <c r="N38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="24"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
       <c r="D39" s="39"/>
       <c r="E39" s="39"/>
       <c r="F39" s="39"/>
@@ -7273,19 +7352,19 @@
       <c r="K39" s="39"/>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
-      <c r="N39" s="23"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23" t="n">
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="24" t="n">
         <v>12680</v>
       </c>
-      <c r="Q39" s="42" t="n">
+      <c r="Q39" s="41" t="n">
         <v>11420</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
       <c r="D40" s="39"/>
       <c r="E40" s="39"/>
       <c r="F40" s="39"/>
@@ -7296,15 +7375,15 @@
       <c r="K40" s="39"/>
       <c r="L40" s="39"/>
       <c r="M40" s="39"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23" t="n">
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24" t="n">
         <v>1260</v>
       </c>
-      <c r="Q40" s="23"/>
+      <c r="Q40" s="24"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AH54" s="0" t="n">
+      <c r="AH54" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7320,345 +7399,353 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="7.1"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="2" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>630</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>1260</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="0" t="n">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="2" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="2" t="n">
         <v>610</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="0" t="n">
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="2" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="0" t="n">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="0" t="n">
+      <c r="B16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="2" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="0" t="n">
+      <c r="B17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="2" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="0" t="n">
+      <c r="B18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="2" t="n">
         <v>1141</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="n">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="n">
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="n">
+      <c r="C21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="0" t="n">
+      <c r="C22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="2" t="n">
         <v>570</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="2" t="n">
         <v>1083</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="n">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="n">
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C27" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="n">
+      <c r="C27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="0" t="n">
+      <c r="C28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2" t="n">
         <v>190</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="0" t="n">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="2" t="n">
         <v>570</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30" s="2" t="n">
         <v>1026</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="0" t="n">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="n">
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="n">
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C34" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" s="0" t="n">
+      <c r="C34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2" t="n">
         <v>171</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="n">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D35" s="0" t="n">
+      <c r="D35" s="2" t="n">
         <v>513</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="n">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="2" t="n">
         <v>1026</v>
       </c>
     </row>

--- a/158/prob158.xlsx
+++ b/158/prob158.xlsx
@@ -489,12 +489,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -506,30 +506,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -3142,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+        <f aca="false">0.00015+com.sun.star.sheet.addin.analysis.getrandbetween(-10,10)/100000</f>
         <v>0.00021</v>
       </c>
       <c r="H4" s="30" t="s">
@@ -3158,14 +3134,14 @@
         <v>22</v>
       </c>
       <c r="E5" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
+        <f aca="false">E$4+com.sun.star.sheet.addin.analysis.getrandbetween(-100,100)/1000</f>
         <v>0.51</v>
       </c>
       <c r="F5" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+        <f aca="false">0.00015+com.sun.star.sheet.addin.analysis.getrandbetween(-10,10)/100000</f>
         <v>5E-005</v>
       </c>
       <c r="H5" s="30" t="s">
@@ -3181,14 +3157,14 @@
         <v>23</v>
       </c>
       <c r="E6" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
+        <f aca="false">E$4+com.sun.star.sheet.addin.analysis.getrandbetween(-100,100)/1000</f>
         <v>0.553</v>
       </c>
       <c r="F6" s="33" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+        <f aca="false">0.00015+com.sun.star.sheet.addin.analysis.getrandbetween(-10,10)/100000</f>
         <v>0.00023</v>
       </c>
       <c r="H6" s="30" t="s">
@@ -3211,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+        <f aca="false">0.00015+com.sun.star.sheet.addin.analysis.getrandbetween(-10,10)/100000</f>
         <v>0.00015</v>
       </c>
       <c r="H7" s="30" t="s">
@@ -3227,14 +3203,14 @@
         <v>25</v>
       </c>
       <c r="E8" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
+        <f aca="false">E$4+com.sun.star.sheet.addin.analysis.getrandbetween(-100,100)/1000</f>
         <v>0.423</v>
       </c>
       <c r="F8" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+        <f aca="false">0.00015+com.sun.star.sheet.addin.analysis.getrandbetween(-10,10)/100000</f>
         <v>0.00023</v>
       </c>
       <c r="H8" s="33" t="n">
@@ -3250,14 +3226,14 @@
         <v>26</v>
       </c>
       <c r="E9" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
+        <f aca="false">E$4+com.sun.star.sheet.addin.analysis.getrandbetween(-100,100)/1000</f>
         <v>0.49</v>
       </c>
       <c r="F9" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+        <f aca="false">0.00015+com.sun.star.sheet.addin.analysis.getrandbetween(-10,10)/100000</f>
         <v>0.00025</v>
       </c>
       <c r="H9" s="30" t="s">
@@ -3273,14 +3249,14 @@
         <v>27</v>
       </c>
       <c r="E10" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
+        <f aca="false">E$4+com.sun.star.sheet.addin.analysis.getrandbetween(-100,100)/1000</f>
         <v>0.544</v>
       </c>
       <c r="F10" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+        <f aca="false">0.00015+com.sun.star.sheet.addin.analysis.getrandbetween(-10,10)/100000</f>
         <v>9E-005</v>
       </c>
       <c r="H10" s="30" t="s">
@@ -3296,14 +3272,14 @@
         <v>28</v>
       </c>
       <c r="E11" s="32" t="n">
-        <f aca="false">E$4+com.sun.star.sheet.addin.Analysis.getRandbetween(-100,100)/1000</f>
+        <f aca="false">E$4+com.sun.star.sheet.addin.analysis.getrandbetween(-100,100)/1000</f>
         <v>0.603</v>
       </c>
       <c r="F11" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="30" t="n">
-        <f aca="false">0.00015+com.sun.star.sheet.addin.Analysis.getRandbetween(-10,10)/100000</f>
+        <f aca="false">0.00015+com.sun.star.sheet.addin.analysis.getrandbetween(-10,10)/100000</f>
         <v>0.0002</v>
       </c>
       <c r="H11" s="30" t="s">
@@ -3336,7 +3312,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q58"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="11.79"/>
@@ -5332,7 +5308,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AK54"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="4.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="5.07"/>
@@ -6701,13 +6677,6 @@
         <v>231</v>
       </c>
       <c r="Q22" s="23"/>
-      <c r="AA22" s="41"/>
-      <c r="AB22" s="41"/>
-      <c r="AC22" s="41"/>
-      <c r="AD22" s="41"/>
-      <c r="AE22" s="41"/>
-      <c r="AF22" s="41"/>
-      <c r="AG22" s="41"/>
       <c r="AJ22" s="0" t="n">
         <f aca="false">SUM(AJ2:AJ21)</f>
         <v>10573</v>
@@ -6748,13 +6717,6 @@
         <v>171</v>
       </c>
       <c r="Q23" s="23"/>
-      <c r="AA23" s="41"/>
-      <c r="AB23" s="41"/>
-      <c r="AC23" s="41"/>
-      <c r="AD23" s="41"/>
-      <c r="AE23" s="41"/>
-      <c r="AF23" s="41"/>
-      <c r="AG23" s="41"/>
       <c r="AJ23" s="0" t="n">
         <f aca="false">AK22-AJ22</f>
         <v>847</v>
@@ -6792,13 +6754,6 @@
         <v>0</v>
       </c>
       <c r="Q24" s="23"/>
-      <c r="AA24" s="41"/>
-      <c r="AB24" s="41"/>
-      <c r="AC24" s="41"/>
-      <c r="AD24" s="41"/>
-      <c r="AE24" s="41"/>
-      <c r="AF24" s="41"/>
-      <c r="AG24" s="41"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="n">
@@ -6832,13 +6787,6 @@
         <v>190</v>
       </c>
       <c r="Q25" s="23"/>
-      <c r="AA25" s="41"/>
-      <c r="AB25" s="41"/>
-      <c r="AC25" s="41"/>
-      <c r="AD25" s="41"/>
-      <c r="AE25" s="41"/>
-      <c r="AF25" s="41"/>
-      <c r="AG25" s="41"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="n">
@@ -6872,13 +6820,6 @@
         <v>210</v>
       </c>
       <c r="Q26" s="23"/>
-      <c r="AA26" s="41"/>
-      <c r="AB26" s="41"/>
-      <c r="AC26" s="41"/>
-      <c r="AD26" s="41"/>
-      <c r="AE26" s="41"/>
-      <c r="AF26" s="41"/>
-      <c r="AG26" s="41"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23"/>
@@ -6910,13 +6851,6 @@
         <v>0</v>
       </c>
       <c r="Q27" s="23"/>
-      <c r="AA27" s="41"/>
-      <c r="AB27" s="41"/>
-      <c r="AC27" s="41"/>
-      <c r="AD27" s="41"/>
-      <c r="AE27" s="41"/>
-      <c r="AF27" s="41"/>
-      <c r="AG27" s="41"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23"/>
@@ -7278,7 +7212,7 @@
       <c r="P39" s="23" t="n">
         <v>12680</v>
       </c>
-      <c r="Q39" s="42" t="n">
+      <c r="Q39" s="41" t="n">
         <v>11420</v>
       </c>
     </row>
@@ -7325,7 +7259,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -7333,57 +7267,57 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="42" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="42" t="n">
         <v>630</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="42" t="n">
         <v>1260</v>
       </c>
     </row>
@@ -7399,46 +7333,46 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="B9" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="42" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="B11" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="42" t="n">
         <v>610</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="0" t="n">
+      <c r="B12" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="42" t="n">
         <v>1200</v>
       </c>
     </row>
@@ -7465,35 +7399,35 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="0" t="n">
+      <c r="B16" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="42" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="0" t="n">
+      <c r="B17" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="42" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="0" t="n">
+      <c r="B18" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="42" t="n">
         <v>1141</v>
       </c>
     </row>
@@ -7531,24 +7465,24 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="42" t="n">
         <v>570</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="42" t="n">
         <v>1083</v>
       </c>
     </row>
@@ -7597,13 +7531,13 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30" s="42" t="n">
         <v>1026</v>
       </c>
     </row>
